--- a/src/main/resources/excel_data/fact_data.xlsx
+++ b/src/main/resources/excel_data/fact_data.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\Drools\cust-info-loader\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\Bamoe\SKT-BAMOE-POC\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06C7157-EF82-415A-B5B8-D226F5534E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E904ECBA-1406-4041-848D-1C8506261EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="cust_scrb" sheetId="1" r:id="rId1"/>
+    <sheet name="cust_svc" sheetId="4" r:id="rId1"/>
     <sheet name="cust_prod" sheetId="2" r:id="rId2"/>
     <sheet name="eqp_mdl" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -39,39 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="223">
-  <si>
-    <t>7000000002</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>NA00006405</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>C1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>9903101000000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>N0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>29</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>NA00002020</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="270">
   <si>
     <t>NA00000262</t>
   </si>
@@ -653,79 +621,244 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>A3D4</t>
+    <t>SVC_MGMT_NUM</t>
+  </si>
+  <si>
+    <t>SVC_NUM</t>
+  </si>
+  <si>
+    <t>FEE_PROD_ID</t>
+  </si>
+  <si>
+    <t>SVC_TYP_CD</t>
+  </si>
+  <si>
+    <t>SVC_DTL_CL_CD</t>
+  </si>
+  <si>
+    <t>CUST_TYP_CD</t>
+  </si>
+  <si>
+    <t>CUST_DTL_TYP_CD</t>
+  </si>
+  <si>
+    <t>PROD_TYP_CD</t>
+  </si>
+  <si>
+    <t>PROD_ID</t>
+  </si>
+  <si>
+    <t>PROD_NM</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>T</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>01030003647</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>AC</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>일반</t>
+  </si>
+  <si>
+    <t>NA00006405</t>
+  </si>
+  <si>
+    <t>010</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>WFGF6N12MR</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>9903101000000</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>N0</t>
+  </si>
+  <si>
+    <t>02</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>CNTRCT_MGMT_NUM</t>
+  </si>
+  <si>
+    <t>USE_CNTRCT_CL_CD</t>
+  </si>
+  <si>
+    <t>USE_CNTRCT_ST_CD</t>
+  </si>
+  <si>
+    <t>CNTRCT_DT</t>
+  </si>
+  <si>
+    <t>CO_CL_CD</t>
+  </si>
+  <si>
+    <t>TAX_BILL_ISUE_YN</t>
+  </si>
+  <si>
+    <t>NM_CUST_NUM</t>
+  </si>
+  <si>
+    <t>ACNT_NUM</t>
+  </si>
+  <si>
+    <t>SVC_CD</t>
+  </si>
+  <si>
+    <t>SVC_ST_CD</t>
+  </si>
+  <si>
+    <t>SVC_ST_CHG_CD</t>
+  </si>
+  <si>
+    <t>SVC_CHG_RSN_CD</t>
+  </si>
+  <si>
+    <t>SVC_TYP_NM</t>
+  </si>
+  <si>
+    <t>SVC_SCRB_DT</t>
+  </si>
+  <si>
+    <t>SCRB_REQ_RSN_CD</t>
+  </si>
+  <si>
+    <t>SVC_TERM_DT</t>
+  </si>
+  <si>
+    <t>IDNT_NUM_CD</t>
+  </si>
+  <si>
+    <t>GRTM_CL_CD</t>
+  </si>
+  <si>
+    <t>WLF_DC_CD</t>
+  </si>
+  <si>
+    <t>WLF_DC_NM</t>
+  </si>
+  <si>
+    <t>WEB_MBR_SCRB_CL_CD</t>
+  </si>
+  <si>
+    <t>WEB_MBR_REQ_AGREE_YN</t>
+  </si>
+  <si>
+    <t>EQP_SER_NUM</t>
+  </si>
+  <si>
+    <t>SIM_SER_NUM</t>
+  </si>
+  <si>
+    <t>EQP_USG_CD</t>
+  </si>
+  <si>
+    <t>EQP_MTHD_CD</t>
+  </si>
+  <si>
+    <t>REL_SVC_MGMT_NUM</t>
+  </si>
+  <si>
+    <t>REL_FEE_PROD_ID</t>
+  </si>
+  <si>
+    <t>CTZ_CORP_BIZ_SER_NUM</t>
+  </si>
+  <si>
+    <t>CTZ_CORP_BIZ_NUM_PINF</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>ACNT_TYP_CD</t>
+  </si>
+  <si>
+    <t>PAY_MTHD_CD</t>
+  </si>
+  <si>
+    <t>SCRB_DT</t>
+  </si>
+  <si>
+    <t>PROD_TERM_RSN_CD</t>
+  </si>
+  <si>
+    <t>EQP_VER_NUM</t>
+  </si>
+  <si>
+    <t>EQP_MGMT_ST_CD</t>
+  </si>
+  <si>
+    <t>MKTG_DT</t>
+  </si>
+  <si>
+    <t>NW_MTHD_CD</t>
+  </si>
+  <si>
+    <t>NATE_CL_CD</t>
+  </si>
+  <si>
+    <t>AUTH_KEY_NUM</t>
+  </si>
+  <si>
+    <t>TRK_IDX_NUM</t>
+  </si>
+  <si>
+    <t>INT_PHON_STA_CL_CD</t>
+  </si>
+  <si>
+    <t>KIT_MDL_CD</t>
+  </si>
+  <si>
+    <t>KIT_SER_NUM</t>
+  </si>
+  <si>
+    <t>N</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SVC_MGMT_NUM</t>
-  </si>
-  <si>
-    <t>SVC_NUM</t>
-  </si>
-  <si>
-    <t>FEE_PROD_ID</t>
-  </si>
-  <si>
-    <t>SVC_TYP_CD</t>
-  </si>
-  <si>
-    <t>SVC_DTL_CL_CD</t>
-  </si>
-  <si>
-    <t>BIRTH_DT</t>
-  </si>
-  <si>
-    <t>CUST_TYP_CD</t>
-  </si>
-  <si>
-    <t>CUST_DTL_TYP_CD</t>
-  </si>
-  <si>
-    <t>ADD_PROD_CNT</t>
-  </si>
-  <si>
-    <t>PROD_TYP_CD</t>
-  </si>
-  <si>
-    <t>PROD_ID</t>
-  </si>
-  <si>
-    <t>PROD_NM</t>
-  </si>
-  <si>
-    <t>SVC_TERM_DT</t>
+    <t>7518308200</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>20250101</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>20250201</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>99991231</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>20251231</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SVC_SCBR_DT</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>PROD_LST</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>01070015678</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>01070025678</t>
+    <t>7308834145</t>
+  </si>
+  <si>
+    <t>7308834145</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -733,7 +866,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -788,8 +921,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -799,6 +939,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -836,7 +982,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -847,6 +993,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1130,141 +1283,368 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF206814-8498-4C24-B0CC-9A078A86DC60}">
+  <dimension ref="A1:BB2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="18.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11" style="6" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13" style="6" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19" style="6" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="21.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="22.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="8.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="18.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13" style="6" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="11.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="14.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="52" max="53" width="11" style="6" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="55" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>202</v>
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>221</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="AT1" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="AW1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="BB1" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B2" s="7">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D2" s="7">
+        <v>20191016</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F2" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="G2" s="7">
+        <v>8004717566</v>
+      </c>
+      <c r="H2" s="7">
+        <v>6443419447</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="N2" s="7">
+        <v>1</v>
+      </c>
+      <c r="O2" s="7">
+        <v>1</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q2" s="7">
+        <v>20191016</v>
+      </c>
+      <c r="R2" s="7">
+        <v>1</v>
+      </c>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="V2" s="7">
+        <v>2</v>
+      </c>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="AA2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC2" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="AF2" s="7"/>
+      <c r="AG2" s="7"/>
+      <c r="AH2" s="7">
+        <v>147670000</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="AJ2" s="7">
+        <v>27</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="AN2" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="AO2" s="7">
+        <v>20220404</v>
+      </c>
+      <c r="AP2" s="7"/>
+      <c r="AQ2" s="7" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>7000000001</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="AR2" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="AT2" s="7">
+        <v>20211008</v>
+      </c>
+      <c r="AU2" s="7">
+        <v>12</v>
+      </c>
+      <c r="AV2" s="7" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>218</v>
-      </c>
+      <c r="AW2" s="7"/>
+      <c r="AX2" s="7"/>
+      <c r="AY2" s="7"/>
+      <c r="AZ2" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="BA2" s="7"/>
+      <c r="BB2" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1275,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7B9F7E-E74E-4E37-9250-8BE4E84EB485}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" style="1" bestFit="1" customWidth="1"/>
@@ -1293,450 +1673,422 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>213</v>
-      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>7000000001</v>
+      <c r="A2" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B2" s="1">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>7000000001</v>
+      <c r="A3" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B3" s="1">
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>7000000001</v>
+      <c r="A4" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>7000000001</v>
+      <c r="A5" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>7000000001</v>
+      <c r="A6" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>7000000001</v>
+      <c r="A7" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7000000001</v>
+      <c r="A8" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>7000000001</v>
+      <c r="A9" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>7000000001</v>
+      <c r="A10" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B10" s="1">
         <v>3</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>7000000001</v>
+      <c r="A11" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B11" s="1">
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>7000000001</v>
+      <c r="A12" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>7000000001</v>
+      <c r="A13" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>7000000001</v>
+      <c r="A14" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B14" s="1">
         <v>3</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>7000000001</v>
+      <c r="A15" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B15" s="1">
         <v>3</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>7000000001</v>
+      <c r="A16" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>7000000001</v>
+      <c r="A17" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B17" s="1">
         <v>3</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>7000000001</v>
+      <c r="A18" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B18" s="1">
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>7000000001</v>
+      <c r="A19" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>7000000001</v>
+      <c r="A20" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B20" s="1">
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>7000000001</v>
+      <c r="A21" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B21" s="1">
         <v>3</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>7000000001</v>
+      <c r="A22" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B22" s="1">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>7000000001</v>
+      <c r="A23" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B23" s="1">
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>7000000001</v>
+      <c r="A24" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>7000000001</v>
+      <c r="A25" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B25" s="1">
         <v>3</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>7000000001</v>
+      <c r="A26" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B26" s="1">
         <v>3</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>7000000001</v>
+      <c r="A27" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B27" s="1">
         <v>3</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>7000000001</v>
+      <c r="A28" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B28" s="1">
         <v>3</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>7000000001</v>
+      <c r="A29" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B29" s="1">
         <v>3</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>7000000001</v>
+      <c r="A30" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="B30" s="1">
         <v>3</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="1">
-        <v>3</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" s="1">
-        <v>3</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1765,2325 +2117,2325 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D2" s="4">
         <v>108</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F2" s="4">
         <v>1</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D3" s="4">
         <v>473</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F3" s="4">
         <v>1</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D4" s="4">
         <v>470</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D5" s="4">
         <v>552</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D6" s="4">
         <v>455</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D7" s="4">
         <v>482</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F7" s="4">
         <v>2</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D8" s="4">
         <v>433</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D9" s="4">
         <v>423</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D10" s="4">
         <v>533</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D11" s="4">
         <v>475</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D12" s="4">
         <v>49</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D13" s="4">
         <v>84</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F13" s="4">
         <v>1</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D14" s="4">
         <v>492</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F14" s="4">
         <v>3</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D15" s="4">
         <v>548</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F15" s="4">
         <v>3</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D16" s="4">
         <v>464</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F16" s="4">
         <v>1</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D17" s="4">
         <v>15</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F17" s="4">
         <v>0</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D18" s="4">
         <v>469</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F18" s="4">
         <v>1</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D19" s="4">
         <v>484</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F19" s="4">
         <v>3</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D20" s="4">
         <v>68</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F20" s="4">
         <v>0</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D21" s="4">
         <v>500</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F21" s="4">
         <v>1</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D22" s="4">
         <v>116</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F22" s="4">
         <v>1</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D23" s="4">
         <v>447</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F23" s="4">
         <v>2</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D24" s="4">
         <v>471</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F24" s="4">
         <v>1</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D25" s="4">
         <v>559</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F25" s="4">
         <v>2</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D26" s="4">
         <v>521</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F26" s="4">
         <v>1</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D27" s="4">
         <v>53</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F27" s="4">
         <v>0</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D28" s="4">
         <v>477</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F28" s="4">
         <v>1</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D29" s="4">
         <v>525</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F29" s="4">
         <v>5</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D30" s="4">
         <v>522</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F30" s="4">
         <v>1</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D31" s="4">
         <v>528</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F31" s="4">
         <v>1</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D32" s="4">
         <v>534</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F32" s="4">
         <v>4</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D33" s="4">
         <v>490</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F33" s="4">
         <v>5</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D34" s="4">
         <v>536</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F34" s="4">
         <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D35" s="4">
         <v>13</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F35" s="4">
         <v>1</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D36" s="4">
         <v>444</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F36" s="4">
         <v>2</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D37" s="4">
         <v>535</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F37" s="4">
         <v>1</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D38" s="4">
         <v>474</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F38" s="4">
         <v>1</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D39" s="4">
         <v>79</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F39" s="4">
         <v>1</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D40" s="4">
         <v>41</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F40" s="4">
         <v>1</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D41" s="4">
         <v>511</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="F41" s="4">
         <v>1</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D42" s="4">
         <v>527</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F42" s="4">
         <v>2</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D43" s="4">
         <v>445</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F43" s="4">
         <v>1</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D44" s="4">
         <v>526</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F44" s="4">
         <v>1</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D45" s="4">
         <v>516</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F45" s="4">
         <v>4</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D46" s="4">
         <v>485</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F46" s="4">
         <v>1</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D47" s="4">
         <v>523</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F47" s="4">
         <v>2</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D48" s="4">
         <v>59</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F48" s="4">
         <v>1</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D49" s="4">
         <v>540</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F49" s="4">
         <v>2</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D50" s="4">
         <v>542</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F50" s="4">
         <v>1</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D51" s="4">
         <v>472</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F51" s="4">
         <v>1</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D52" s="4">
         <v>61</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F52" s="4">
         <v>1</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D53" s="4">
         <v>44</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F53" s="4">
         <v>1</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D54" s="4">
         <v>64</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F54" s="4">
         <v>1</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D55" s="4">
         <v>58</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F55" s="4">
         <v>1</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D56" s="4">
         <v>31</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F56" s="4">
         <v>2</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D57" s="4">
         <v>47</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F57" s="4">
         <v>1</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D58" s="4">
         <v>402</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F58" s="4">
         <v>1</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D59" s="4">
         <v>418</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F59" s="4">
         <v>1</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D60" s="4">
         <v>422</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F60" s="4">
         <v>1</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D61" s="4">
         <v>427</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F61" s="4">
         <v>5</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D62" s="4">
         <v>440</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F62" s="4">
         <v>2</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D63" s="4">
         <v>442</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F63" s="4">
         <v>2</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D64" s="4">
         <v>91</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F64" s="4">
         <v>1</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D65" s="4">
         <v>425</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F65" s="4">
         <v>2</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D66" s="4">
         <v>431</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F66" s="4">
         <v>1</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D67" s="4">
         <v>436</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F67" s="4">
         <v>1</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D68" s="4">
         <v>460</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F68" s="4">
         <v>1</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D69" s="4">
         <v>404</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F69" s="4">
         <v>2</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D70" s="4">
         <v>421</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F70" s="4">
         <v>1</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D71" s="4">
         <v>89</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F71" s="4">
         <v>1</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D72" s="4">
         <v>543</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F72" s="4">
         <v>2</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D73" s="4">
         <v>513</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F73" s="4">
         <v>1</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D74" s="4">
         <v>435</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F74" s="4">
         <v>1</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D75" s="4">
         <v>498</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F75" s="4">
         <v>1</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D76" s="4">
         <v>556</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F76" s="4">
         <v>2</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D77" s="4">
         <v>555</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F77" s="4">
         <v>2</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D78" s="4">
         <v>557</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F78" s="4">
         <v>2</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D79" s="4">
         <v>489</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F79" s="4">
         <v>2</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D80" s="4">
         <v>539</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F80" s="4">
         <v>1</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D81" s="4">
         <v>538</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F81" s="4">
         <v>3</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D82" s="4">
         <v>512</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F82" s="4">
         <v>1</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D83" s="4">
         <v>507</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="F83" s="4">
         <v>1</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D84" s="4">
         <v>509</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F84" s="4">
         <v>1</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D85" s="4">
         <v>544</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F85" s="4">
         <v>1</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D86" s="4">
         <v>529</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F86" s="4">
         <v>1</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D87" s="4">
         <v>40</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F87" s="4">
         <v>1</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D88" s="4">
         <v>39</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F88" s="4">
         <v>7</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D89" s="4">
         <v>491</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F89" s="4">
         <v>4</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D90" s="4">
         <v>465</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F90" s="4">
         <v>2</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D91" s="4">
         <v>35</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F91" s="4">
         <v>1</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D92" s="4">
         <v>54</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F92" s="4">
         <v>3</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D93" s="4">
         <v>88</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F93" s="4">
         <v>1</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D94" s="4">
         <v>417</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F94" s="4">
         <v>1</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D95" s="4">
         <v>419</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F95" s="4">
         <v>1</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D96" s="4">
         <v>426</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F96" s="4">
         <v>1</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D97" s="4">
         <v>439</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F97" s="4">
         <v>2</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D98" s="4">
         <v>441</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F98" s="4">
         <v>2</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D99" s="4">
         <v>443</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F99" s="4">
         <v>2</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D100" s="4">
         <v>56</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="F100" s="4">
         <v>9</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D101" s="4">
         <v>532</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F101" s="4">
         <v>1</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/excel_data/fact_data.xlsx
+++ b/src/main/resources/excel_data/fact_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\Bamoe\SKT-BAMOE-POC\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E904ECBA-1406-4041-848D-1C8506261EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBEBD26-F6CC-423C-9869-4ECDC2C14093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="272">
   <si>
     <t>NA00000262</t>
   </si>
@@ -859,6 +859,14 @@
   </si>
   <si>
     <t>7308834145</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>BEF_FEE_PROD_ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA00008154</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1284,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF206814-8498-4C24-B0CC-9A078A86DC60}">
-  <dimension ref="A1:BB2"/>
+  <dimension ref="A1:BC2"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.75" style="6" bestFit="1" customWidth="1"/>
@@ -1339,10 +1347,11 @@
     <col min="51" max="51" width="19.25" style="6" bestFit="1" customWidth="1"/>
     <col min="52" max="53" width="11" style="6" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="12.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="55" max="16384" width="9" style="6"/>
+    <col min="55" max="55" width="14.375" style="6" customWidth="1"/>
+    <col min="56" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>221</v>
       </c>
@@ -1505,8 +1514,11 @@
       <c r="BB1" s="2" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="BC1" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>267</v>
       </c>
@@ -1563,7 +1575,7 @@
       </c>
       <c r="S2" s="7"/>
       <c r="T2" s="7" t="s">
-        <v>211</v>
+        <v>271</v>
       </c>
       <c r="U2" s="7" t="s">
         <v>212</v>
@@ -1641,10 +1653,13 @@
       <c r="AX2" s="7"/>
       <c r="AY2" s="7"/>
       <c r="AZ2" s="7" t="s">
-        <v>211</v>
+        <v>271</v>
       </c>
       <c r="BA2" s="7"/>
       <c r="BB2" s="7"/>
+      <c r="BC2" s="7" t="s">
+        <v>211</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/src/main/resources/excel_data/fact_data.xlsx
+++ b/src/main/resources/excel_data/fact_data.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\Bamoe\SKT-BAMOE-POC\src\main\resources\excel_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\260429\SKT-BAMOE-POC\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBEBD26-F6CC-423C-9869-4ECDC2C14093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704BEED1-48DD-4865-A1AD-7A6B0724EDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cust_svc" sheetId="4" r:id="rId1"/>
     <sheet name="cust_prod" sheetId="2" r:id="rId2"/>
     <sheet name="eqp_mdl" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="349">
   <si>
     <t>NA00000262</t>
   </si>
@@ -618,7 +619,7 @@
   </si>
   <si>
     <t>00</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SVC_MGMT_NUM</t>
@@ -655,7 +656,7 @@
   </si>
   <si>
     <t>T</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>N</t>
@@ -665,11 +666,11 @@
   </si>
   <si>
     <t>01030003647</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>AC</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>F4</t>
@@ -682,7 +683,7 @@
   </si>
   <si>
     <t>010</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WFGF6N12MR</t>
@@ -695,18 +696,18 @@
   </si>
   <si>
     <t>9903101000000</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>01</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>N0</t>
   </si>
   <si>
     <t>02</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>C1</t>
@@ -848,38 +849,280 @@
   </si>
   <si>
     <t>N</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>7518308200</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>7308834145</t>
   </si>
   <si>
     <t>7308834145</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>BEF_FEE_PROD_ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>NA00008154</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ITM0000020</t>
+  </si>
+  <si>
+    <t>권한자여부</t>
+  </si>
+  <si>
+    <t>NGMAUA025,NGMAUA024</t>
+  </si>
+  <si>
+    <t>ITM0000022</t>
+  </si>
+  <si>
+    <t>서비스변경코드</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>ITM0000023</t>
+  </si>
+  <si>
+    <t>취소여부</t>
+  </si>
+  <si>
+    <t>ITM0000032</t>
+  </si>
+  <si>
+    <t>단말그룹포함여부</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>ITM0000051</t>
+  </si>
+  <si>
+    <t>채널구분코드</t>
+  </si>
+  <si>
+    <t>NGM</t>
+  </si>
+  <si>
+    <t>ITM0000073</t>
+  </si>
+  <si>
+    <t>로밍사용여부</t>
+  </si>
+  <si>
+    <t>ITM0000074</t>
+  </si>
+  <si>
+    <t>상품그룹존재여부</t>
+  </si>
+  <si>
+    <t>ITM0000078</t>
+  </si>
+  <si>
+    <t>온라인배치구분코드</t>
+  </si>
+  <si>
+    <t>ONLINE</t>
+  </si>
+  <si>
+    <t>ITM0000084</t>
+  </si>
+  <si>
+    <t>업무처리서비스트랜잭션ID</t>
+  </si>
+  <si>
+    <t>ZORDSS0400380_TR01</t>
+  </si>
+  <si>
+    <t>ITM0000114</t>
+  </si>
+  <si>
+    <t>변경사유코드</t>
+  </si>
+  <si>
+    <t>ITM0000173</t>
+  </si>
+  <si>
+    <t>충전사용여부</t>
+  </si>
+  <si>
+    <t>ITM0000189</t>
+  </si>
+  <si>
+    <t>T할부지원변경가능요금제여부</t>
+  </si>
+  <si>
+    <t>ITM0000220</t>
+  </si>
+  <si>
+    <t>처리내용2</t>
+  </si>
+  <si>
+    <t>ITM0000241</t>
+  </si>
+  <si>
+    <t>상품그룹추가단말존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000253</t>
+  </si>
+  <si>
+    <t>조건유형존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000259</t>
+  </si>
+  <si>
+    <t>추가단말정의존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000319</t>
+  </si>
+  <si>
+    <t>요금변경당일3회가능여부</t>
+  </si>
+  <si>
+    <t>ITM0000322</t>
+  </si>
+  <si>
+    <t>명의고객별.INEE가입가능여부</t>
+  </si>
+  <si>
+    <t>ITM0000323</t>
+  </si>
+  <si>
+    <t>명의고객별TING가입가능여부</t>
+  </si>
+  <si>
+    <t>ITM0000694</t>
+  </si>
+  <si>
+    <t>요금상품그룹추가기준상품존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000762</t>
+  </si>
+  <si>
+    <t>사이버요금변경3회SKIP여부</t>
+  </si>
+  <si>
+    <t>ITM0000794</t>
+  </si>
+  <si>
+    <t>추가단말상품그룹존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000889</t>
+  </si>
+  <si>
+    <t>당일해지이력존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000900</t>
+  </si>
+  <si>
+    <t>팅번호이동해지존재여부</t>
+  </si>
+  <si>
+    <t>ITM0000914</t>
+  </si>
+  <si>
+    <t>기기변경구분코드</t>
+  </si>
+  <si>
+    <t>ITM0000919</t>
+  </si>
+  <si>
+    <t>특정상품가입해지구분코드</t>
+  </si>
+  <si>
+    <t>ITM0000924</t>
+  </si>
+  <si>
+    <t>T지원금약정가입여부</t>
+  </si>
+  <si>
+    <t>ITM0000952</t>
+  </si>
+  <si>
+    <t>무선상품처리대상건수</t>
+  </si>
+  <si>
+    <t>ITM0000976</t>
+  </si>
+  <si>
+    <t>애플워치개통진행중여부</t>
+  </si>
+  <si>
+    <t>ITM0001021</t>
+  </si>
+  <si>
+    <t>사업용용도코드</t>
+  </si>
+  <si>
+    <t>ITM0001031</t>
+  </si>
+  <si>
+    <t>DS단말중복불가상품사용여부</t>
+  </si>
+  <si>
+    <t>ITM0001050</t>
+  </si>
+  <si>
+    <t>T지원금약정사용여부</t>
+  </si>
+  <si>
+    <t>ITM0001052</t>
+  </si>
+  <si>
+    <t>언택트_가입_기변_이력체크</t>
+  </si>
+  <si>
+    <t>ITM0001125</t>
+  </si>
+  <si>
+    <t>T지원금약정승계_가능여부</t>
+  </si>
+  <si>
+    <t>CON_ITM_VAL</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CON_ITM_NM</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CON_ITEM_ID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -981,8 +1224,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -990,31 +1236,33 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{1A717BD2-B117-41DF-8DA6-5E651CD0CD22}"/>
     <cellStyle name="표준 3" xfId="2" xr:uid="{982C4383-5604-4E87-8C51-8BC13ADFFAE7}"/>
+    <cellStyle name="표준 4" xfId="3" xr:uid="{A9A67573-2BD5-43F1-81FB-DE9C2B34982D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1662,7 +1910,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -2107,7 +2355,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -4454,7 +4702,398 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3747A4-993E-4CA6-B3B1-148509345593}">
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.875" style="9" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/src/main/resources/excel_data/fact_data.xlsx
+++ b/src/main/resources/excel_data/fact_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\260429\SKT-BAMOE-POC\src\main\resources\excel_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\Drools\cust-info-loader\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704BEED1-48DD-4865-A1AD-7A6B0724EDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C294609E-19DC-4858-9DBF-C9D0EF12476B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="cust_svc" sheetId="4" r:id="rId1"/>
     <sheet name="cust_prod" sheetId="2" r:id="rId2"/>
     <sheet name="eqp_mdl" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
+    <sheet name="cons_itm_val" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -880,228 +880,229 @@
     <t>NGMAUA025,NGMAUA024</t>
   </si>
   <si>
+    <t>서비스변경코드</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>ITM0000023</t>
+  </si>
+  <si>
+    <t>취소여부</t>
+  </si>
+  <si>
+    <t>ITM0000032</t>
+  </si>
+  <si>
+    <t>단말그룹포함여부</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>ITM0000051</t>
+  </si>
+  <si>
+    <t>채널구분코드</t>
+  </si>
+  <si>
+    <t>NGM</t>
+  </si>
+  <si>
+    <t>ITM0000073</t>
+  </si>
+  <si>
+    <t>로밍사용여부</t>
+  </si>
+  <si>
+    <t>ITM0000074</t>
+  </si>
+  <si>
+    <t>상품그룹존재여부</t>
+  </si>
+  <si>
+    <t>ITM0000078</t>
+  </si>
+  <si>
+    <t>온라인배치구분코드</t>
+  </si>
+  <si>
+    <t>ONLINE</t>
+  </si>
+  <si>
+    <t>ITM0000084</t>
+  </si>
+  <si>
+    <t>업무처리서비스트랜잭션ID</t>
+  </si>
+  <si>
+    <t>ZORDSS0400380_TR01</t>
+  </si>
+  <si>
+    <t>ITM0000114</t>
+  </si>
+  <si>
+    <t>변경사유코드</t>
+  </si>
+  <si>
+    <t>ITM0000173</t>
+  </si>
+  <si>
+    <t>충전사용여부</t>
+  </si>
+  <si>
+    <t>ITM0000189</t>
+  </si>
+  <si>
+    <t>T할부지원변경가능요금제여부</t>
+  </si>
+  <si>
+    <t>ITM0000220</t>
+  </si>
+  <si>
+    <t>처리내용2</t>
+  </si>
+  <si>
+    <t>ITM0000241</t>
+  </si>
+  <si>
+    <t>상품그룹추가단말존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000253</t>
+  </si>
+  <si>
+    <t>조건유형존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000259</t>
+  </si>
+  <si>
+    <t>추가단말정의존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000319</t>
+  </si>
+  <si>
+    <t>요금변경당일3회가능여부</t>
+  </si>
+  <si>
+    <t>ITM0000322</t>
+  </si>
+  <si>
+    <t>명의고객별.INEE가입가능여부</t>
+  </si>
+  <si>
+    <t>ITM0000323</t>
+  </si>
+  <si>
+    <t>명의고객별TING가입가능여부</t>
+  </si>
+  <si>
+    <t>ITM0000694</t>
+  </si>
+  <si>
+    <t>요금상품그룹추가기준상품존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000762</t>
+  </si>
+  <si>
+    <t>사이버요금변경3회SKIP여부</t>
+  </si>
+  <si>
+    <t>ITM0000794</t>
+  </si>
+  <si>
+    <t>추가단말상품그룹존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000889</t>
+  </si>
+  <si>
+    <t>당일해지이력존제여부</t>
+  </si>
+  <si>
+    <t>ITM0000900</t>
+  </si>
+  <si>
+    <t>팅번호이동해지존재여부</t>
+  </si>
+  <si>
+    <t>ITM0000914</t>
+  </si>
+  <si>
+    <t>기기변경구분코드</t>
+  </si>
+  <si>
+    <t>ITM0000919</t>
+  </si>
+  <si>
+    <t>특정상품가입해지구분코드</t>
+  </si>
+  <si>
+    <t>ITM0000924</t>
+  </si>
+  <si>
+    <t>T지원금약정가입여부</t>
+  </si>
+  <si>
+    <t>ITM0000952</t>
+  </si>
+  <si>
+    <t>무선상품처리대상건수</t>
+  </si>
+  <si>
+    <t>ITM0000976</t>
+  </si>
+  <si>
+    <t>애플워치개통진행중여부</t>
+  </si>
+  <si>
+    <t>ITM0001021</t>
+  </si>
+  <si>
+    <t>사업용용도코드</t>
+  </si>
+  <si>
+    <t>ITM0001031</t>
+  </si>
+  <si>
+    <t>DS단말중복불가상품사용여부</t>
+  </si>
+  <si>
+    <t>ITM0001050</t>
+  </si>
+  <si>
+    <t>T지원금약정사용여부</t>
+  </si>
+  <si>
+    <t>ITM0001052</t>
+  </si>
+  <si>
+    <t>언택트_가입_기변_이력체크</t>
+  </si>
+  <si>
+    <t>ITM0001125</t>
+  </si>
+  <si>
+    <t>T지원금약정승계_가능여부</t>
+  </si>
+  <si>
     <t>ITM0000022</t>
-  </si>
-  <si>
-    <t>서비스변경코드</t>
-  </si>
-  <si>
-    <t>G1</t>
-  </si>
-  <si>
-    <t>ITM0000023</t>
-  </si>
-  <si>
-    <t>취소여부</t>
-  </si>
-  <si>
-    <t>ITM0000032</t>
-  </si>
-  <si>
-    <t>단말그룹포함여부</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>ITM0000051</t>
-  </si>
-  <si>
-    <t>채널구분코드</t>
-  </si>
-  <si>
-    <t>NGM</t>
-  </si>
-  <si>
-    <t>ITM0000073</t>
-  </si>
-  <si>
-    <t>로밍사용여부</t>
-  </si>
-  <si>
-    <t>ITM0000074</t>
-  </si>
-  <si>
-    <t>상품그룹존재여부</t>
-  </si>
-  <si>
-    <t>ITM0000078</t>
-  </si>
-  <si>
-    <t>온라인배치구분코드</t>
-  </si>
-  <si>
-    <t>ONLINE</t>
-  </si>
-  <si>
-    <t>ITM0000084</t>
-  </si>
-  <si>
-    <t>업무처리서비스트랜잭션ID</t>
-  </si>
-  <si>
-    <t>ZORDSS0400380_TR01</t>
-  </si>
-  <si>
-    <t>ITM0000114</t>
-  </si>
-  <si>
-    <t>변경사유코드</t>
-  </si>
-  <si>
-    <t>ITM0000173</t>
-  </si>
-  <si>
-    <t>충전사용여부</t>
-  </si>
-  <si>
-    <t>ITM0000189</t>
-  </si>
-  <si>
-    <t>T할부지원변경가능요금제여부</t>
-  </si>
-  <si>
-    <t>ITM0000220</t>
-  </si>
-  <si>
-    <t>처리내용2</t>
-  </si>
-  <si>
-    <t>ITM0000241</t>
-  </si>
-  <si>
-    <t>상품그룹추가단말존제여부</t>
-  </si>
-  <si>
-    <t>ITM0000253</t>
-  </si>
-  <si>
-    <t>조건유형존제여부</t>
-  </si>
-  <si>
-    <t>ITM0000259</t>
-  </si>
-  <si>
-    <t>추가단말정의존제여부</t>
-  </si>
-  <si>
-    <t>ITM0000319</t>
-  </si>
-  <si>
-    <t>요금변경당일3회가능여부</t>
-  </si>
-  <si>
-    <t>ITM0000322</t>
-  </si>
-  <si>
-    <t>명의고객별.INEE가입가능여부</t>
-  </si>
-  <si>
-    <t>ITM0000323</t>
-  </si>
-  <si>
-    <t>명의고객별TING가입가능여부</t>
-  </si>
-  <si>
-    <t>ITM0000694</t>
-  </si>
-  <si>
-    <t>요금상품그룹추가기준상품존제여부</t>
-  </si>
-  <si>
-    <t>ITM0000762</t>
-  </si>
-  <si>
-    <t>사이버요금변경3회SKIP여부</t>
-  </si>
-  <si>
-    <t>ITM0000794</t>
-  </si>
-  <si>
-    <t>추가단말상품그룹존제여부</t>
-  </si>
-  <si>
-    <t>ITM0000889</t>
-  </si>
-  <si>
-    <t>당일해지이력존제여부</t>
-  </si>
-  <si>
-    <t>ITM0000900</t>
-  </si>
-  <si>
-    <t>팅번호이동해지존재여부</t>
-  </si>
-  <si>
-    <t>ITM0000914</t>
-  </si>
-  <si>
-    <t>기기변경구분코드</t>
-  </si>
-  <si>
-    <t>ITM0000919</t>
-  </si>
-  <si>
-    <t>특정상품가입해지구분코드</t>
-  </si>
-  <si>
-    <t>ITM0000924</t>
-  </si>
-  <si>
-    <t>T지원금약정가입여부</t>
-  </si>
-  <si>
-    <t>ITM0000952</t>
-  </si>
-  <si>
-    <t>무선상품처리대상건수</t>
-  </si>
-  <si>
-    <t>ITM0000976</t>
-  </si>
-  <si>
-    <t>애플워치개통진행중여부</t>
-  </si>
-  <si>
-    <t>ITM0001021</t>
-  </si>
-  <si>
-    <t>사업용용도코드</t>
-  </si>
-  <si>
-    <t>ITM0001031</t>
-  </si>
-  <si>
-    <t>DS단말중복불가상품사용여부</t>
-  </si>
-  <si>
-    <t>ITM0001050</t>
-  </si>
-  <si>
-    <t>T지원금약정사용여부</t>
-  </si>
-  <si>
-    <t>ITM0001052</t>
-  </si>
-  <si>
-    <t>언택트_가입_기변_이력체크</t>
-  </si>
-  <si>
-    <t>ITM0001125</t>
-  </si>
-  <si>
-    <t>T지원금약정승계_가능여부</t>
-  </si>
-  <si>
-    <t>CON_ITM_VAL</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>CON_ITM_NM</t>
+    <t>CONS_ITM_NM</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>CON_ITEM_ID</t>
+    <t>CONS_ITM_VAL</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CONS_ITM_ID</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -4724,10 +4725,10 @@
         <v>348</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4743,21 +4744,21 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="C3" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>278</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>279</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>205</v>
@@ -4765,32 +4766,32 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>281</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>286</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>287</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>205</v>
@@ -4798,10 +4799,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>288</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>289</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>205</v>
@@ -4809,32 +4810,32 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>291</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>296</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>297</v>
       </c>
       <c r="C11" s="9">
         <v>0</v>
@@ -4842,10 +4843,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>298</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>299</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>205</v>
@@ -4853,29 +4854,29 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>301</v>
-      </c>
       <c r="C13" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>302</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>304</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>305</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>205</v>
@@ -4883,21 +4884,21 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>307</v>
-      </c>
       <c r="C16" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>308</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>309</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>205</v>
@@ -4905,21 +4906,21 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>311</v>
-      </c>
       <c r="C18" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>312</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>313</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>205</v>
@@ -4927,10 +4928,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>314</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>315</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>205</v>
@@ -4938,10 +4939,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>316</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>317</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>205</v>
@@ -4949,10 +4950,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>318</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>319</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>205</v>
@@ -4960,10 +4961,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>320</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>321</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>205</v>
@@ -4971,10 +4972,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>322</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>323</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>205</v>
@@ -4982,10 +4983,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>324</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>325</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>205</v>
@@ -4993,26 +4994,26 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>326</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>328</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>330</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>331</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>205</v>
@@ -5020,10 +5021,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>332</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="C29" s="9">
         <v>0</v>
@@ -5031,10 +5032,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>334</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>335</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>205</v>
@@ -5042,18 +5043,18 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>336</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>338</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>339</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>205</v>
@@ -5061,10 +5062,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>340</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>341</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>205</v>
@@ -5072,21 +5073,21 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>343</v>
-      </c>
       <c r="C34" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>344</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>345</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>205</v>

--- a/src/main/resources/excel_data/fact_data.xlsx
+++ b/src/main/resources/excel_data/fact_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\Drools\cust-info-loader\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C294609E-19DC-4858-9DBF-C9D0EF12476B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A967B23-D3EE-4795-97F4-68E7BA05A66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cust_svc" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="389">
   <si>
     <t>NA00000262</t>
   </si>
@@ -1104,6 +1104,158 @@
   <si>
     <t>CONS_ITM_ID</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCRB_TERM_CL_CD</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>09</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>0 청년 다이렉트 69(T 우주)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA00006405</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>5GX플래티넘</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUTO_OP_CL_CD</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>049</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>084</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>015</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>068</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>053</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>013</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>079</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>041</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>059</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>061</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>044</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>064</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>058</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>031</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>047</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>091</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>089</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>040</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>039</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>035</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>054</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>088</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>056</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>07</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1389,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1258,6 +1410,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1625,7 +1781,7 @@
       <c r="H1" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>193</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -1807,11 +1963,11 @@
       <c r="M2" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="N2" s="7">
-        <v>1</v>
-      </c>
-      <c r="O2" s="7">
-        <v>1</v>
+      <c r="N2" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>356</v>
       </c>
       <c r="P2" s="7" t="s">
         <v>210</v>
@@ -1883,8 +2039,8 @@
       <c r="AQ2" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="AR2" s="7">
-        <v>0</v>
+      <c r="AR2" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="AS2" s="7" t="s">
         <v>219</v>
@@ -1919,15 +2075,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7B9F7E-E74E-4E37-9250-8BE4E84EB485}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.25" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.375" style="1" bestFit="1" customWidth="1"/>
@@ -1935,7 +2090,7 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>193</v>
       </c>
@@ -1948,411 +2103,631 @@
       <c r="D1" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="12">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="12" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="E2" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="12">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="E3" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="12">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="E4" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="12">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="E5" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="12">
         <v>3</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="12" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="E6" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="12">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="E7" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="12">
         <v>3</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="12" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="E8" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="12">
         <v>2</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="E9" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="12">
         <v>3</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="E10" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="12">
         <v>3</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="12" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="E11" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="12">
         <v>3</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="12" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="E12" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="12">
         <v>3</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="12" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="E13" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="12">
         <v>3</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="E14" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="12">
         <v>3</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="12" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="E15" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="12">
         <v>3</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="12" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="E16" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="12">
         <v>3</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="E17" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="12">
         <v>3</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="12" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="E18" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="12">
         <v>3</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="12" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="E19" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="12">
         <v>3</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="E20" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="12">
         <v>3</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="E21" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="12">
         <v>2</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="12" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="E22" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="12">
         <v>2</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="12" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="E23" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="12">
         <v>2</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="12" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="E24" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="12">
         <v>3</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="12" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="E25" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="12">
         <v>3</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="12" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="E26" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="12">
         <v>3</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="12" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="E27" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="12">
         <v>3</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="12" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="E28" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="12">
         <v>3</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="12" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="E29" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="12">
         <v>3</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="12" t="s">
         <v>57</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2364,7 +2739,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EE70DE6-A972-46D3-82F7-7E3FDFA6EAC4}">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.625" style="3" bestFit="1" customWidth="1"/>
@@ -2379,7 +2754,7 @@
     <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>58</v>
       </c>
@@ -2402,7 +2777,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -2418,14 +2793,16 @@
       <c r="E2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="4">
-        <v>1</v>
+      <c r="F2" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>65</v>
       </c>
@@ -2441,14 +2818,16 @@
       <c r="E3" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="4">
-        <v>1</v>
+      <c r="F3" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>65</v>
       </c>
@@ -2464,14 +2843,16 @@
       <c r="E4" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="4">
-        <v>1</v>
+      <c r="F4" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>65</v>
       </c>
@@ -2487,14 +2868,16 @@
       <c r="E5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F5" s="4">
-        <v>1</v>
+      <c r="F5" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>65</v>
       </c>
@@ -2510,14 +2893,16 @@
       <c r="E6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="4">
-        <v>4</v>
+      <c r="F6" s="4" t="s">
+        <v>385</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>65</v>
       </c>
@@ -2533,14 +2918,16 @@
       <c r="E7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="4">
-        <v>2</v>
+      <c r="F7" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>65</v>
       </c>
@@ -2556,14 +2943,16 @@
       <c r="E8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="4">
-        <v>1</v>
+      <c r="F8" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>65</v>
       </c>
@@ -2579,14 +2968,16 @@
       <c r="E9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F9" s="4">
-        <v>1</v>
+      <c r="F9" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>65</v>
       </c>
@@ -2602,14 +2993,16 @@
       <c r="E10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F10" s="4">
-        <v>1</v>
+      <c r="F10" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>65</v>
       </c>
@@ -2625,14 +3018,16 @@
       <c r="E11" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="4">
-        <v>1</v>
+      <c r="F11" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>65</v>
       </c>
@@ -2642,20 +3037,22 @@
       <c r="C12" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D12" s="4">
-        <v>49</v>
+      <c r="D12" s="4" t="s">
+        <v>362</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="4">
-        <v>1</v>
+      <c r="F12" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>65</v>
       </c>
@@ -2665,20 +3062,22 @@
       <c r="C13" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D13" s="4">
-        <v>84</v>
+      <c r="D13" s="4" t="s">
+        <v>363</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F13" s="4">
-        <v>1</v>
+      <c r="F13" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>65</v>
       </c>
@@ -2694,14 +3093,16 @@
       <c r="E14" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="4">
-        <v>3</v>
+      <c r="F14" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>65</v>
       </c>
@@ -2717,14 +3118,16 @@
       <c r="E15" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="4">
-        <v>3</v>
+      <c r="F15" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>65</v>
       </c>
@@ -2740,14 +3143,16 @@
       <c r="E16" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F16" s="4">
-        <v>1</v>
+      <c r="F16" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>65</v>
       </c>
@@ -2757,20 +3162,22 @@
       <c r="C17" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D17" s="4">
-        <v>15</v>
+      <c r="D17" s="4" t="s">
+        <v>364</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="4">
-        <v>0</v>
+      <c r="F17" s="4" t="s">
+        <v>352</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>65</v>
       </c>
@@ -2786,14 +3193,16 @@
       <c r="E18" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F18" s="4">
-        <v>1</v>
+      <c r="F18" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>65</v>
       </c>
@@ -2809,14 +3218,16 @@
       <c r="E19" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="4">
-        <v>3</v>
+      <c r="F19" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>65</v>
       </c>
@@ -2826,20 +3237,22 @@
       <c r="C20" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D20" s="4">
-        <v>68</v>
+      <c r="D20" s="4" t="s">
+        <v>365</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F20" s="4">
-        <v>0</v>
+      <c r="F20" s="4" t="s">
+        <v>352</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>65</v>
       </c>
@@ -2855,14 +3268,16 @@
       <c r="E21" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F21" s="4">
-        <v>1</v>
+      <c r="F21" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>65</v>
       </c>
@@ -2878,14 +3293,16 @@
       <c r="E22" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="4">
-        <v>1</v>
+      <c r="F22" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>65</v>
       </c>
@@ -2901,14 +3318,16 @@
       <c r="E23" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="4">
-        <v>2</v>
+      <c r="F23" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>65</v>
       </c>
@@ -2924,14 +3343,16 @@
       <c r="E24" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="4">
-        <v>1</v>
+      <c r="F24" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>65</v>
       </c>
@@ -2947,14 +3368,16 @@
       <c r="E25" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F25" s="4">
-        <v>2</v>
+      <c r="F25" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>65</v>
       </c>
@@ -2970,14 +3393,16 @@
       <c r="E26" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="4">
-        <v>1</v>
+      <c r="F26" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>65</v>
       </c>
@@ -2987,20 +3412,22 @@
       <c r="C27" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="4">
-        <v>53</v>
+      <c r="D27" s="4" t="s">
+        <v>366</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F27" s="4">
-        <v>0</v>
+      <c r="F27" s="4" t="s">
+        <v>352</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>65</v>
       </c>
@@ -3016,14 +3443,16 @@
       <c r="E28" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="4">
-        <v>1</v>
+      <c r="F28" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>65</v>
       </c>
@@ -3039,14 +3468,16 @@
       <c r="E29" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F29" s="4">
-        <v>5</v>
+      <c r="F29" s="4" t="s">
+        <v>387</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>65</v>
       </c>
@@ -3062,14 +3493,16 @@
       <c r="E30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="4">
-        <v>1</v>
+      <c r="F30" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>65</v>
       </c>
@@ -3085,14 +3518,16 @@
       <c r="E31" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F31" s="4">
-        <v>1</v>
+      <c r="F31" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>65</v>
       </c>
@@ -3108,14 +3543,16 @@
       <c r="E32" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F32" s="4">
-        <v>4</v>
+      <c r="F32" s="4" t="s">
+        <v>385</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>65</v>
       </c>
@@ -3131,14 +3568,16 @@
       <c r="E33" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="F33" s="4">
-        <v>5</v>
+      <c r="F33" s="4" t="s">
+        <v>387</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>65</v>
       </c>
@@ -3154,14 +3593,16 @@
       <c r="E34" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F34" s="4">
-        <v>1</v>
+      <c r="F34" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>65</v>
       </c>
@@ -3171,20 +3612,22 @@
       <c r="C35" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D35" s="4">
-        <v>13</v>
+      <c r="D35" s="4" t="s">
+        <v>367</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F35" s="4">
-        <v>1</v>
+      <c r="F35" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>65</v>
       </c>
@@ -3200,14 +3643,16 @@
       <c r="E36" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F36" s="4">
-        <v>2</v>
+      <c r="F36" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>65</v>
       </c>
@@ -3223,14 +3668,16 @@
       <c r="E37" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="F37" s="4">
-        <v>1</v>
+      <c r="F37" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>65</v>
       </c>
@@ -3246,14 +3693,16 @@
       <c r="E38" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="4">
-        <v>1</v>
+      <c r="F38" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>65</v>
       </c>
@@ -3263,20 +3712,22 @@
       <c r="C39" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D39" s="4">
-        <v>79</v>
+      <c r="D39" s="4" t="s">
+        <v>368</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F39" s="4">
-        <v>1</v>
+      <c r="F39" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>65</v>
       </c>
@@ -3286,20 +3737,22 @@
       <c r="C40" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D40" s="4">
-        <v>41</v>
+      <c r="D40" s="4" t="s">
+        <v>369</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F40" s="4">
-        <v>1</v>
+      <c r="F40" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>65</v>
       </c>
@@ -3315,14 +3768,16 @@
       <c r="E41" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F41" s="4">
-        <v>1</v>
+      <c r="F41" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>65</v>
       </c>
@@ -3338,14 +3793,16 @@
       <c r="E42" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F42" s="4">
-        <v>2</v>
+      <c r="F42" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>65</v>
       </c>
@@ -3361,14 +3818,16 @@
       <c r="E43" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F43" s="4">
-        <v>1</v>
+      <c r="F43" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>65</v>
       </c>
@@ -3384,14 +3843,16 @@
       <c r="E44" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F44" s="4">
-        <v>1</v>
+      <c r="F44" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>65</v>
       </c>
@@ -3407,14 +3868,16 @@
       <c r="E45" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="F45" s="4">
-        <v>4</v>
+      <c r="F45" s="4" t="s">
+        <v>385</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>65</v>
       </c>
@@ -3430,14 +3893,16 @@
       <c r="E46" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F46" s="4">
-        <v>1</v>
+      <c r="F46" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>65</v>
       </c>
@@ -3453,14 +3918,16 @@
       <c r="E47" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F47" s="4">
-        <v>2</v>
+      <c r="F47" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>65</v>
       </c>
@@ -3470,20 +3937,22 @@
       <c r="C48" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D48" s="4">
-        <v>59</v>
+      <c r="D48" s="4" t="s">
+        <v>370</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F48" s="4">
-        <v>1</v>
+      <c r="F48" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>65</v>
       </c>
@@ -3499,14 +3968,16 @@
       <c r="E49" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F49" s="4">
-        <v>2</v>
+      <c r="F49" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>65</v>
       </c>
@@ -3522,14 +3993,16 @@
       <c r="E50" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F50" s="4">
-        <v>1</v>
+      <c r="F50" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>65</v>
       </c>
@@ -3545,14 +4018,16 @@
       <c r="E51" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F51" s="4">
-        <v>1</v>
+      <c r="F51" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>65</v>
       </c>
@@ -3562,20 +4037,22 @@
       <c r="C52" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D52" s="4">
-        <v>61</v>
+      <c r="D52" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F52" s="4">
-        <v>1</v>
+      <c r="F52" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>65</v>
       </c>
@@ -3585,20 +4062,22 @@
       <c r="C53" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D53" s="4">
-        <v>44</v>
+      <c r="D53" s="4" t="s">
+        <v>372</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F53" s="4">
-        <v>1</v>
+      <c r="F53" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>65</v>
       </c>
@@ -3608,20 +4087,22 @@
       <c r="C54" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D54" s="4">
-        <v>64</v>
+      <c r="D54" s="4" t="s">
+        <v>373</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F54" s="4">
-        <v>1</v>
+      <c r="F54" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>65</v>
       </c>
@@ -3631,20 +4112,22 @@
       <c r="C55" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D55" s="4">
-        <v>58</v>
+      <c r="D55" s="4" t="s">
+        <v>374</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F55" s="4">
-        <v>1</v>
+      <c r="F55" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>65</v>
       </c>
@@ -3654,20 +4137,22 @@
       <c r="C56" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D56" s="4">
-        <v>31</v>
+      <c r="D56" s="4" t="s">
+        <v>375</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F56" s="4">
-        <v>2</v>
+      <c r="F56" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>65</v>
       </c>
@@ -3677,20 +4162,22 @@
       <c r="C57" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D57" s="4">
-        <v>47</v>
+      <c r="D57" s="4" t="s">
+        <v>376</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F57" s="4">
-        <v>1</v>
+      <c r="F57" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>65</v>
       </c>
@@ -3706,14 +4193,16 @@
       <c r="E58" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F58" s="4">
-        <v>1</v>
+      <c r="F58" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>65</v>
       </c>
@@ -3729,14 +4218,16 @@
       <c r="E59" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F59" s="4">
-        <v>1</v>
+      <c r="F59" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>65</v>
       </c>
@@ -3752,14 +4243,16 @@
       <c r="E60" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="F60" s="4">
-        <v>1</v>
+      <c r="F60" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I60" s="10"/>
+      <c r="J60" s="10"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>65</v>
       </c>
@@ -3775,14 +4268,16 @@
       <c r="E61" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F61" s="4">
-        <v>5</v>
+      <c r="F61" s="4" t="s">
+        <v>387</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>65</v>
       </c>
@@ -3798,14 +4293,16 @@
       <c r="E62" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F62" s="4">
-        <v>2</v>
+      <c r="F62" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I62" s="10"/>
+      <c r="J62" s="10"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>65</v>
       </c>
@@ -3821,14 +4318,16 @@
       <c r="E63" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F63" s="4">
-        <v>2</v>
+      <c r="F63" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I63" s="10"/>
+      <c r="J63" s="10"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>65</v>
       </c>
@@ -3838,20 +4337,22 @@
       <c r="C64" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D64" s="4">
-        <v>91</v>
+      <c r="D64" s="4" t="s">
+        <v>377</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F64" s="4">
-        <v>1</v>
+      <c r="F64" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I64" s="10"/>
+      <c r="J64" s="10"/>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>65</v>
       </c>
@@ -3867,14 +4368,16 @@
       <c r="E65" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F65" s="4">
-        <v>2</v>
+      <c r="F65" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>65</v>
       </c>
@@ -3890,14 +4393,16 @@
       <c r="E66" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F66" s="4">
-        <v>1</v>
+      <c r="F66" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>65</v>
       </c>
@@ -3913,14 +4418,16 @@
       <c r="E67" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F67" s="4">
-        <v>1</v>
+      <c r="F67" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>65</v>
       </c>
@@ -3936,14 +4443,16 @@
       <c r="E68" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="F68" s="4">
-        <v>1</v>
+      <c r="F68" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I68" s="10"/>
+      <c r="J68" s="10"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>65</v>
       </c>
@@ -3959,14 +4468,16 @@
       <c r="E69" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F69" s="4">
-        <v>2</v>
+      <c r="F69" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I69" s="10"/>
+      <c r="J69" s="10"/>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>65</v>
       </c>
@@ -3982,14 +4493,16 @@
       <c r="E70" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F70" s="4">
-        <v>1</v>
+      <c r="F70" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I70" s="10"/>
+      <c r="J70" s="10"/>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>65</v>
       </c>
@@ -3999,20 +4512,22 @@
       <c r="C71" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D71" s="4">
-        <v>89</v>
+      <c r="D71" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="F71" s="4">
-        <v>1</v>
+      <c r="F71" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I71" s="10"/>
+      <c r="J71" s="10"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>65</v>
       </c>
@@ -4028,14 +4543,16 @@
       <c r="E72" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="F72" s="4">
-        <v>2</v>
+      <c r="F72" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I72" s="10"/>
+      <c r="J72" s="10"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>65</v>
       </c>
@@ -4051,14 +4568,16 @@
       <c r="E73" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F73" s="4">
-        <v>1</v>
+      <c r="F73" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>65</v>
       </c>
@@ -4074,14 +4593,16 @@
       <c r="E74" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F74" s="4">
-        <v>1</v>
+      <c r="F74" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I74" s="10"/>
+      <c r="J74" s="10"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>65</v>
       </c>
@@ -4097,14 +4618,16 @@
       <c r="E75" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F75" s="4">
-        <v>1</v>
+      <c r="F75" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I75" s="10"/>
+      <c r="J75" s="10"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>65</v>
       </c>
@@ -4120,14 +4643,16 @@
       <c r="E76" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F76" s="4">
-        <v>2</v>
+      <c r="F76" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I76" s="10"/>
+      <c r="J76" s="10"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>65</v>
       </c>
@@ -4143,14 +4668,16 @@
       <c r="E77" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="F77" s="4">
-        <v>2</v>
+      <c r="F77" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I77" s="10"/>
+      <c r="J77" s="10"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>65</v>
       </c>
@@ -4166,14 +4693,16 @@
       <c r="E78" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="F78" s="4">
-        <v>2</v>
+      <c r="F78" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I78" s="10"/>
+      <c r="J78" s="10"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>65</v>
       </c>
@@ -4189,14 +4718,16 @@
       <c r="E79" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="F79" s="4">
-        <v>2</v>
+      <c r="F79" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I79" s="10"/>
+      <c r="J79" s="10"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>65</v>
       </c>
@@ -4212,14 +4743,16 @@
       <c r="E80" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F80" s="4">
-        <v>1</v>
+      <c r="F80" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I80" s="10"/>
+      <c r="J80" s="10"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
         <v>65</v>
       </c>
@@ -4235,14 +4768,16 @@
       <c r="E81" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="F81" s="4">
-        <v>3</v>
+      <c r="F81" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>65</v>
       </c>
@@ -4258,14 +4793,16 @@
       <c r="E82" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F82" s="4">
-        <v>1</v>
+      <c r="F82" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I82" s="10"/>
+      <c r="J82" s="10"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>65</v>
       </c>
@@ -4281,14 +4818,16 @@
       <c r="E83" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="F83" s="4">
-        <v>1</v>
+      <c r="F83" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I83" s="10"/>
+      <c r="J83" s="10"/>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>65</v>
       </c>
@@ -4304,14 +4843,16 @@
       <c r="E84" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="F84" s="4">
-        <v>1</v>
+      <c r="F84" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I84" s="10"/>
+      <c r="J84" s="10"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>65</v>
       </c>
@@ -4327,14 +4868,16 @@
       <c r="E85" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="F85" s="4">
-        <v>1</v>
+      <c r="F85" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I85" s="10"/>
+      <c r="J85" s="10"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>65</v>
       </c>
@@ -4350,14 +4893,16 @@
       <c r="E86" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="F86" s="4">
-        <v>1</v>
+      <c r="F86" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I86" s="10"/>
+      <c r="J86" s="10"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>65</v>
       </c>
@@ -4367,20 +4912,22 @@
       <c r="C87" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D87" s="4">
-        <v>40</v>
+      <c r="D87" s="4" t="s">
+        <v>379</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F87" s="4">
-        <v>1</v>
+      <c r="F87" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I87" s="10"/>
+      <c r="J87" s="10"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
         <v>65</v>
       </c>
@@ -4390,20 +4937,22 @@
       <c r="C88" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D88" s="4">
-        <v>39</v>
+      <c r="D88" s="4" t="s">
+        <v>380</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="F88" s="4">
-        <v>7</v>
+      <c r="F88" s="4" t="s">
+        <v>388</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I88" s="10"/>
+      <c r="J88" s="10"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>65</v>
       </c>
@@ -4419,14 +4968,16 @@
       <c r="E89" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="F89" s="4">
-        <v>4</v>
+      <c r="F89" s="4" t="s">
+        <v>385</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I89" s="10"/>
+      <c r="J89" s="10"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>65</v>
       </c>
@@ -4442,14 +4993,16 @@
       <c r="E90" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="F90" s="4">
-        <v>2</v>
+      <c r="F90" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I90" s="10"/>
+      <c r="J90" s="10"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>65</v>
       </c>
@@ -4459,20 +5012,22 @@
       <c r="C91" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D91" s="4">
-        <v>35</v>
+      <c r="D91" s="4" t="s">
+        <v>381</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F91" s="4">
-        <v>1</v>
+      <c r="F91" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I91" s="10"/>
+      <c r="J91" s="10"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>65</v>
       </c>
@@ -4482,20 +5037,22 @@
       <c r="C92" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D92" s="4">
-        <v>54</v>
+      <c r="D92" s="4" t="s">
+        <v>382</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F92" s="4">
-        <v>3</v>
+      <c r="F92" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I92" s="10"/>
+      <c r="J92" s="10"/>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>65</v>
       </c>
@@ -4505,20 +5062,22 @@
       <c r="C93" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D93" s="4">
-        <v>88</v>
+      <c r="D93" s="4" t="s">
+        <v>383</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="F93" s="4">
-        <v>1</v>
+      <c r="F93" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G93" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I93" s="10"/>
+      <c r="J93" s="10"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>65</v>
       </c>
@@ -4534,14 +5093,16 @@
       <c r="E94" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F94" s="4">
-        <v>1</v>
+      <c r="F94" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I94" s="10"/>
+      <c r="J94" s="10"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>65</v>
       </c>
@@ -4557,14 +5118,16 @@
       <c r="E95" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="F95" s="4">
-        <v>1</v>
+      <c r="F95" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I95" s="10"/>
+      <c r="J95" s="10"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>65</v>
       </c>
@@ -4580,14 +5143,16 @@
       <c r="E96" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F96" s="4">
-        <v>1</v>
+      <c r="F96" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I96" s="10"/>
+      <c r="J96" s="10"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>65</v>
       </c>
@@ -4603,14 +5168,16 @@
       <c r="E97" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="F97" s="4">
-        <v>2</v>
+      <c r="F97" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I97" s="10"/>
+      <c r="J97" s="10"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>65</v>
       </c>
@@ -4626,14 +5193,16 @@
       <c r="E98" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="F98" s="4">
-        <v>2</v>
+      <c r="F98" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I98" s="10"/>
+      <c r="J98" s="10"/>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>65</v>
       </c>
@@ -4649,14 +5218,16 @@
       <c r="E99" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="F99" s="4">
-        <v>2</v>
+      <c r="F99" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I99" s="10"/>
+      <c r="J99" s="10"/>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>65</v>
       </c>
@@ -4666,20 +5237,22 @@
       <c r="C100" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D100" s="4">
-        <v>56</v>
+      <c r="D100" s="4" t="s">
+        <v>384</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="F100" s="4">
-        <v>9</v>
+      <c r="F100" s="4" t="s">
+        <v>350</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I100" s="10"/>
+      <c r="J100" s="10"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>65</v>
       </c>
@@ -4695,12 +5268,14 @@
       <c r="E101" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F101" s="4">
-        <v>1</v>
+      <c r="F101" s="4" t="s">
+        <v>355</v>
       </c>
       <c r="G101" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="I101" s="10"/>
+      <c r="J101" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -4732,364 +5307,368 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="11" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="11" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="11" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="11" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="11" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="11" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="11" t="s">
         <v>302</v>
       </c>
+      <c r="C14" s="11"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="11" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="11" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="11" t="s">
         <v>326</v>
       </c>
+      <c r="C26" s="11"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="11" t="s">
         <v>328</v>
       </c>
+      <c r="C27" s="11"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="11" t="s">
         <v>336</v>
       </c>
+      <c r="C31" s="11"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="11" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="9" t="s">
+      <c r="A34" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="11" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="11" t="s">
         <v>205</v>
       </c>
     </row>

--- a/src/main/resources/excel_data/fact_data.xlsx
+++ b/src/main/resources/excel_data/fact_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\Drools\cust-info-loader\src\main\resources\excel_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\260429\SKT-BAMOE-POC\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A967B23-D3EE-4795-97F4-68E7BA05A66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45818A38-D3F4-4DDA-9FA6-833A8B4C16EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cust_svc" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="389">
   <si>
     <t>NA00000262</t>
   </si>
@@ -877,9 +877,6 @@
     <t>권한자여부</t>
   </si>
   <si>
-    <t>NGMAUA025,NGMAUA024</t>
-  </si>
-  <si>
     <t>서비스변경코드</t>
   </si>
   <si>
@@ -1256,6 +1253,10 @@
   </si>
   <si>
     <t>07</t>
+  </si>
+  <si>
+    <t>ORDAU5992</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1964,10 +1965,10 @@
         <v>209</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P2" s="7" t="s">
         <v>210</v>
@@ -2104,10 +2105,10 @@
         <v>202</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,7 +2125,7 @@
         <v>29</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>192</v>
@@ -2144,7 +2145,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>192</v>
@@ -2164,7 +2165,7 @@
         <v>31</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>192</v>
@@ -2184,7 +2185,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>192</v>
@@ -2204,7 +2205,7 @@
         <v>33</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>192</v>
@@ -2224,7 +2225,7 @@
         <v>34</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>192</v>
@@ -2244,7 +2245,7 @@
         <v>35</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>192</v>
@@ -2264,7 +2265,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>192</v>
@@ -2284,7 +2285,7 @@
         <v>37</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>192</v>
@@ -2304,7 +2305,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>192</v>
@@ -2324,7 +2325,7 @@
         <v>39</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>192</v>
@@ -2344,7 +2345,7 @@
         <v>40</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F13" s="12" t="s">
         <v>192</v>
@@ -2364,7 +2365,7 @@
         <v>41</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>192</v>
@@ -2384,7 +2385,7 @@
         <v>42</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>192</v>
@@ -2404,7 +2405,7 @@
         <v>43</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>192</v>
@@ -2424,7 +2425,7 @@
         <v>44</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>192</v>
@@ -2444,7 +2445,7 @@
         <v>45</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F18" s="12" t="s">
         <v>192</v>
@@ -2464,7 +2465,7 @@
         <v>46</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F19" s="12" t="s">
         <v>192</v>
@@ -2484,7 +2485,7 @@
         <v>47</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>192</v>
@@ -2504,7 +2505,7 @@
         <v>48</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F21" s="12" t="s">
         <v>192</v>
@@ -2524,7 +2525,7 @@
         <v>49</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F22" s="12" t="s">
         <v>192</v>
@@ -2544,7 +2545,7 @@
         <v>50</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>192</v>
@@ -2564,7 +2565,7 @@
         <v>51</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>192</v>
@@ -2584,7 +2585,7 @@
         <v>52</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F25" s="12" t="s">
         <v>192</v>
@@ -2604,7 +2605,7 @@
         <v>53</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F26" s="12" t="s">
         <v>192</v>
@@ -2624,7 +2625,7 @@
         <v>54</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F27" s="12" t="s">
         <v>192</v>
@@ -2644,7 +2645,7 @@
         <v>55</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F28" s="12" t="s">
         <v>192</v>
@@ -2664,7 +2665,7 @@
         <v>56</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F29" s="12" t="s">
         <v>192</v>
@@ -2684,7 +2685,7 @@
         <v>57</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F30" s="12" t="s">
         <v>192</v>
@@ -2695,16 +2696,16 @@
         <v>268</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="D31" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="D31" s="12" t="s">
-        <v>358</v>
-      </c>
       <c r="E31" s="12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F31" s="12" t="s">
         <v>192</v>
@@ -2715,16 +2716,16 @@
         <v>268</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>271</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F32" s="12" t="s">
         <v>192</v>
@@ -2794,7 +2795,7 @@
         <v>67</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>68</v>
@@ -2819,7 +2820,7 @@
         <v>69</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>70</v>
@@ -2844,7 +2845,7 @@
         <v>71</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>70</v>
@@ -2869,7 +2870,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>68</v>
@@ -2894,7 +2895,7 @@
         <v>73</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>74</v>
@@ -2919,7 +2920,7 @@
         <v>75</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>76</v>
@@ -2944,7 +2945,7 @@
         <v>77</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>70</v>
@@ -2969,7 +2970,7 @@
         <v>78</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>70</v>
@@ -2994,7 +2995,7 @@
         <v>79</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>70</v>
@@ -3019,7 +3020,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>70</v>
@@ -3038,13 +3039,13 @@
         <v>192</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>81</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>68</v>
@@ -3063,13 +3064,13 @@
         <v>192</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>82</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>68</v>
@@ -3094,7 +3095,7 @@
         <v>83</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>84</v>
@@ -3119,7 +3120,7 @@
         <v>85</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>86</v>
@@ -3144,7 +3145,7 @@
         <v>87</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>68</v>
@@ -3163,13 +3164,13 @@
         <v>192</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>88</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>70</v>
@@ -3194,7 +3195,7 @@
         <v>89</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>70</v>
@@ -3219,7 +3220,7 @@
         <v>90</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>91</v>
@@ -3238,13 +3239,13 @@
         <v>192</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>92</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>70</v>
@@ -3269,7 +3270,7 @@
         <v>93</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>70</v>
@@ -3294,7 +3295,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>68</v>
@@ -3319,7 +3320,7 @@
         <v>95</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>96</v>
@@ -3344,7 +3345,7 @@
         <v>97</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>70</v>
@@ -3369,7 +3370,7 @@
         <v>98</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>96</v>
@@ -3394,7 +3395,7 @@
         <v>99</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>68</v>
@@ -3413,13 +3414,13 @@
         <v>192</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>100</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>70</v>
@@ -3444,7 +3445,7 @@
         <v>101</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>70</v>
@@ -3469,7 +3470,7 @@
         <v>102</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>103</v>
@@ -3494,7 +3495,7 @@
         <v>104</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>68</v>
@@ -3519,7 +3520,7 @@
         <v>105</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>68</v>
@@ -3544,7 +3545,7 @@
         <v>106</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>107</v>
@@ -3569,7 +3570,7 @@
         <v>108</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G33" s="4" t="s">
         <v>109</v>
@@ -3594,7 +3595,7 @@
         <v>110</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G34" s="4" t="s">
         <v>68</v>
@@ -3613,13 +3614,13 @@
         <v>192</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>111</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G35" s="4" t="s">
         <v>70</v>
@@ -3644,7 +3645,7 @@
         <v>112</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G36" s="4" t="s">
         <v>96</v>
@@ -3669,7 +3670,7 @@
         <v>113</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G37" s="4" t="s">
         <v>68</v>
@@ -3694,7 +3695,7 @@
         <v>114</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>68</v>
@@ -3713,13 +3714,13 @@
         <v>192</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>115</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>68</v>
@@ -3738,13 +3739,13 @@
         <v>192</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>116</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>70</v>
@@ -3769,7 +3770,7 @@
         <v>117</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>68</v>
@@ -3794,7 +3795,7 @@
         <v>118</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>119</v>
@@ -3819,7 +3820,7 @@
         <v>120</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>96</v>
@@ -3844,7 +3845,7 @@
         <v>121</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>68</v>
@@ -3869,7 +3870,7 @@
         <v>122</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>123</v>
@@ -3894,7 +3895,7 @@
         <v>124</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>70</v>
@@ -3919,7 +3920,7 @@
         <v>125</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>96</v>
@@ -3938,13 +3939,13 @@
         <v>192</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>126</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>68</v>
@@ -3969,7 +3970,7 @@
         <v>127</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>128</v>
@@ -3994,7 +3995,7 @@
         <v>129</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>68</v>
@@ -4019,7 +4020,7 @@
         <v>130</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>68</v>
@@ -4038,13 +4039,13 @@
         <v>192</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>131</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>70</v>
@@ -4063,13 +4064,13 @@
         <v>192</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>132</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>68</v>
@@ -4088,13 +4089,13 @@
         <v>192</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>70</v>
@@ -4113,13 +4114,13 @@
         <v>192</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>134</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>68</v>
@@ -4138,13 +4139,13 @@
         <v>192</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>136</v>
@@ -4163,13 +4164,13 @@
         <v>192</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>137</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>70</v>
@@ -4194,7 +4195,7 @@
         <v>138</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>139</v>
@@ -4219,7 +4220,7 @@
         <v>140</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>141</v>
@@ -4244,7 +4245,7 @@
         <v>142</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>68</v>
@@ -4269,7 +4270,7 @@
         <v>143</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>144</v>
@@ -4294,7 +4295,7 @@
         <v>145</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>96</v>
@@ -4319,7 +4320,7 @@
         <v>146</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>96</v>
@@ -4338,13 +4339,13 @@
         <v>192</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>147</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>68</v>
@@ -4369,7 +4370,7 @@
         <v>148</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>96</v>
@@ -4394,7 +4395,7 @@
         <v>149</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>68</v>
@@ -4419,7 +4420,7 @@
         <v>150</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>70</v>
@@ -4444,7 +4445,7 @@
         <v>151</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>68</v>
@@ -4469,7 +4470,7 @@
         <v>152</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>96</v>
@@ -4494,7 +4495,7 @@
         <v>153</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>68</v>
@@ -4513,13 +4514,13 @@
         <v>192</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>68</v>
@@ -4544,7 +4545,7 @@
         <v>155</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>96</v>
@@ -4569,7 +4570,7 @@
         <v>156</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>68</v>
@@ -4594,7 +4595,7 @@
         <v>157</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>70</v>
@@ -4619,7 +4620,7 @@
         <v>158</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>70</v>
@@ -4644,7 +4645,7 @@
         <v>159</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>96</v>
@@ -4669,7 +4670,7 @@
         <v>160</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>161</v>
@@ -4694,7 +4695,7 @@
         <v>162</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>96</v>
@@ -4719,7 +4720,7 @@
         <v>163</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>164</v>
@@ -4744,7 +4745,7 @@
         <v>165</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>68</v>
@@ -4769,7 +4770,7 @@
         <v>166</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>167</v>
@@ -4794,7 +4795,7 @@
         <v>168</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>68</v>
@@ -4819,7 +4820,7 @@
         <v>169</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G83" s="4" t="s">
         <v>68</v>
@@ -4844,7 +4845,7 @@
         <v>170</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G84" s="4" t="s">
         <v>70</v>
@@ -4869,7 +4870,7 @@
         <v>171</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G85" s="4" t="s">
         <v>68</v>
@@ -4894,7 +4895,7 @@
         <v>172</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G86" s="4" t="s">
         <v>68</v>
@@ -4913,13 +4914,13 @@
         <v>192</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>173</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G87" s="4" t="s">
         <v>70</v>
@@ -4938,13 +4939,13 @@
         <v>192</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>174</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G88" s="4" t="s">
         <v>175</v>
@@ -4969,7 +4970,7 @@
         <v>176</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G89" s="4" t="s">
         <v>177</v>
@@ -4994,7 +4995,7 @@
         <v>178</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G90" s="4" t="s">
         <v>96</v>
@@ -5013,13 +5014,13 @@
         <v>192</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>179</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G91" s="4" t="s">
         <v>68</v>
@@ -5038,13 +5039,13 @@
         <v>192</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>180</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G92" s="4" t="s">
         <v>181</v>
@@ -5063,13 +5064,13 @@
         <v>192</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>182</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G93" s="4" t="s">
         <v>68</v>
@@ -5094,7 +5095,7 @@
         <v>183</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G94" s="4" t="s">
         <v>68</v>
@@ -5119,7 +5120,7 @@
         <v>184</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G95" s="4" t="s">
         <v>68</v>
@@ -5144,7 +5145,7 @@
         <v>185</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G96" s="4" t="s">
         <v>68</v>
@@ -5169,7 +5170,7 @@
         <v>186</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G97" s="4" t="s">
         <v>96</v>
@@ -5194,7 +5195,7 @@
         <v>187</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>96</v>
@@ -5219,7 +5220,7 @@
         <v>188</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>96</v>
@@ -5238,13 +5239,13 @@
         <v>192</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>189</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G100" s="4" t="s">
         <v>190</v>
@@ -5269,7 +5270,7 @@
         <v>191</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G101" s="4" t="s">
         <v>70</v>
@@ -5297,13 +5298,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5314,26 +5315,26 @@
         <v>273</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>274</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>275</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>277</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>278</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>205</v>
@@ -5341,32 +5342,32 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="11" t="s">
         <v>280</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="11" t="s">
         <v>283</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>285</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>286</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>205</v>
@@ -5374,10 +5375,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>288</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>205</v>
@@ -5385,43 +5386,43 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="11" t="s">
         <v>290</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="11" t="s">
         <v>293</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="C11" s="11">
-        <v>0</v>
+      <c r="C11" s="12" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>297</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>298</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>205</v>
@@ -5429,30 +5430,30 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>300</v>
-      </c>
       <c r="C13" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>301</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>302</v>
       </c>
       <c r="C14" s="11"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>303</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>304</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>205</v>
@@ -5460,21 +5461,21 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>306</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>307</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>308</v>
       </c>
       <c r="C17" s="11" t="s">
         <v>205</v>
@@ -5482,21 +5483,21 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>310</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>311</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>312</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>205</v>
@@ -5504,10 +5505,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>313</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>314</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>205</v>
@@ -5515,10 +5516,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>315</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>316</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>205</v>
@@ -5526,10 +5527,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>317</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>318</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>205</v>
@@ -5537,10 +5538,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>319</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>320</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>205</v>
@@ -5548,10 +5549,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>321</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>322</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>205</v>
@@ -5559,10 +5560,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>323</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>324</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>205</v>
@@ -5570,28 +5571,28 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>325</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>326</v>
       </c>
       <c r="C26" s="11"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>327</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>328</v>
       </c>
       <c r="C27" s="11"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>329</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>330</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>205</v>
@@ -5599,10 +5600,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>331</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>332</v>
       </c>
       <c r="C29" s="11">
         <v>0</v>
@@ -5610,10 +5611,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>333</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>334</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>205</v>
@@ -5621,19 +5622,19 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>335</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>336</v>
       </c>
       <c r="C31" s="11"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>337</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>338</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>205</v>
@@ -5641,10 +5642,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>339</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>340</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>205</v>
@@ -5652,21 +5653,21 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>342</v>
-      </c>
       <c r="C34" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>343</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>344</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>205</v>

--- a/src/main/resources/excel_data/fact_data.xlsx
+++ b/src/main/resources/excel_data/fact_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\260429\SKT-BAMOE-POC\src\main\resources\excel_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keom-ibm/Desktop/Project/skt_bamoe/SKT-BAMOE-POC/src/main/resources/excel_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45818A38-D3F4-4DDA-9FA6-833A8B4C16EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{58798884-D960-6446-931A-074112CF1E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19300" yWindow="22260" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cust_svc" sheetId="4" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="cons_itm_val" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,15 +33,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="390">
   <si>
     <t>NA00000262</t>
   </si>
@@ -1256,7 +1254,9 @@
   </si>
   <si>
     <t>ORDAU5992</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA00008154</t>
   </si>
 </sst>
 </file>
@@ -1267,14 +1267,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1282,7 +1282,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1290,14 +1290,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1305,14 +1305,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1321,14 +1321,14 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1390,7 +1390,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1411,13 +1411,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1" xr:uid="{1A717BD2-B117-41DF-8DA6-5E651CD0CD22}"/>
     <cellStyle name="표준 3" xfId="2" xr:uid="{982C4383-5604-4E87-8C51-8BC13ADFFAE7}"/>
     <cellStyle name="표준 4" xfId="3" xr:uid="{A9A67573-2BD5-43F1-81FB-DE9C2B34982D}"/>
@@ -1699,65 +1698,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF206814-8498-4C24-B0CC-9A078A86DC60}">
   <dimension ref="A1:BC2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="17.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="17.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.5" style="6" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" style="6" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="11" style="6" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="22.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="13" style="6" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="21.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="22.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="15.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="15.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="12.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="8.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="18.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="18.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="13" style="6" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="11.125" style="6" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="14.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="11.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="14.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="52" max="53" width="11" style="6" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="12.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.375" style="6" customWidth="1"/>
+    <col min="54" max="54" width="12.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.33203125" style="6" customWidth="1"/>
     <col min="56" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>221</v>
       </c>
@@ -1924,7 +1923,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:55" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>267</v>
       </c>
@@ -2077,21 +2076,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE7B9F7E-E74E-4E37-9250-8BE4E84EB485}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>193</v>
       </c>
@@ -2111,623 +2109,623 @@
         <v>360</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>3</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="F2" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>3</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="F3" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>3</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="F4" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>3</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="F5" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="F6" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>3</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="F7" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>3</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="F8" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>2</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="F9" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>3</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+      <c r="F10" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>3</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="F11" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>3</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="F12" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>3</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="F13" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>3</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F14" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="F14" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>3</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F15" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="F15" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>3</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F16" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="F16" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>3</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="F17" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>3</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F18" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="F18" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>3</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="F19" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <v>3</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F20" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="F20" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>3</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F21" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
+      <c r="F21" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <v>2</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F22" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="F22" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <v>2</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F23" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
+      <c r="F23" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <v>2</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F24" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+      <c r="F24" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <v>3</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="12" t="s">
+      <c r="F25" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <v>3</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F26" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
+      <c r="F26" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <v>3</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F27" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="12" t="s">
+      <c r="F27" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="11">
         <v>3</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F28" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="F28" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <v>3</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F29" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="s">
+      <c r="F29" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <v>3</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="F30" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="F30" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="11" t="s">
         <v>352</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="F31" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="12" t="s">
+      <c r="F31" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="11" t="s">
         <v>352</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="D32" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="11" t="s">
         <v>192</v>
       </c>
     </row>
@@ -2741,21 +2739,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EE70DE6-A972-46D3-82F7-7E3FDFA6EAC4}">
   <dimension ref="A1:J101"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="9" style="3"/>
     <col min="11" max="11" width="9" style="3" customWidth="1"/>
     <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>58</v>
       </c>
@@ -2778,7 +2776,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>65</v>
       </c>
@@ -2800,10 +2798,10 @@
       <c r="G2" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>65</v>
       </c>
@@ -2825,10 +2823,10 @@
       <c r="G3" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>65</v>
       </c>
@@ -2850,10 +2848,10 @@
       <c r="G4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>65</v>
       </c>
@@ -2875,10 +2873,10 @@
       <c r="G5" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>65</v>
       </c>
@@ -2900,10 +2898,10 @@
       <c r="G6" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>65</v>
       </c>
@@ -2925,10 +2923,10 @@
       <c r="G7" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>65</v>
       </c>
@@ -2950,10 +2948,10 @@
       <c r="G8" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>65</v>
       </c>
@@ -2975,10 +2973,10 @@
       <c r="G9" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>65</v>
       </c>
@@ -3000,10 +2998,10 @@
       <c r="G10" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>65</v>
       </c>
@@ -3025,10 +3023,10 @@
       <c r="G11" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>65</v>
       </c>
@@ -3050,10 +3048,10 @@
       <c r="G12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>65</v>
       </c>
@@ -3075,10 +3073,10 @@
       <c r="G13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>65</v>
       </c>
@@ -3100,10 +3098,10 @@
       <c r="G14" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>65</v>
       </c>
@@ -3125,10 +3123,10 @@
       <c r="G15" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>65</v>
       </c>
@@ -3150,10 +3148,10 @@
       <c r="G16" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>65</v>
       </c>
@@ -3175,10 +3173,10 @@
       <c r="G17" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>65</v>
       </c>
@@ -3200,10 +3198,10 @@
       <c r="G18" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+    </row>
+    <row r="19" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>65</v>
       </c>
@@ -3225,10 +3223,10 @@
       <c r="G19" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>65</v>
       </c>
@@ -3250,10 +3248,10 @@
       <c r="G20" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>65</v>
       </c>
@@ -3275,10 +3273,10 @@
       <c r="G21" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>65</v>
       </c>
@@ -3300,10 +3298,10 @@
       <c r="G22" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>65</v>
       </c>
@@ -3325,10 +3323,10 @@
       <c r="G23" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>65</v>
       </c>
@@ -3350,10 +3348,10 @@
       <c r="G24" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>65</v>
       </c>
@@ -3375,10 +3373,10 @@
       <c r="G25" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+    </row>
+    <row r="26" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>65</v>
       </c>
@@ -3400,10 +3398,10 @@
       <c r="G26" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+    </row>
+    <row r="27" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>65</v>
       </c>
@@ -3425,10 +3423,10 @@
       <c r="G27" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>65</v>
       </c>
@@ -3450,10 +3448,10 @@
       <c r="G28" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>65</v>
       </c>
@@ -3475,10 +3473,10 @@
       <c r="G29" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>65</v>
       </c>
@@ -3500,10 +3498,10 @@
       <c r="G30" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+    </row>
+    <row r="31" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>65</v>
       </c>
@@ -3525,10 +3523,10 @@
       <c r="G31" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>65</v>
       </c>
@@ -3550,10 +3548,10 @@
       <c r="G32" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+    </row>
+    <row r="33" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>65</v>
       </c>
@@ -3575,10 +3573,10 @@
       <c r="G33" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>65</v>
       </c>
@@ -3600,10 +3598,10 @@
       <c r="G34" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>65</v>
       </c>
@@ -3625,10 +3623,10 @@
       <c r="G35" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+    </row>
+    <row r="36" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>65</v>
       </c>
@@ -3650,10 +3648,10 @@
       <c r="G36" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>65</v>
       </c>
@@ -3675,10 +3673,10 @@
       <c r="G37" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>65</v>
       </c>
@@ -3700,10 +3698,10 @@
       <c r="G38" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+    </row>
+    <row r="39" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>65</v>
       </c>
@@ -3725,10 +3723,10 @@
       <c r="G39" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+    </row>
+    <row r="40" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>65</v>
       </c>
@@ -3750,10 +3748,10 @@
       <c r="G40" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+    </row>
+    <row r="41" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>65</v>
       </c>
@@ -3775,10 +3773,10 @@
       <c r="G41" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+    </row>
+    <row r="42" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>65</v>
       </c>
@@ -3800,10 +3798,10 @@
       <c r="G42" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+    </row>
+    <row r="43" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>65</v>
       </c>
@@ -3825,10 +3823,10 @@
       <c r="G43" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+    </row>
+    <row r="44" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>65</v>
       </c>
@@ -3850,10 +3848,10 @@
       <c r="G44" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+    </row>
+    <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>65</v>
       </c>
@@ -3875,10 +3873,10 @@
       <c r="G45" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+    </row>
+    <row r="46" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>65</v>
       </c>
@@ -3900,10 +3898,10 @@
       <c r="G46" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+    </row>
+    <row r="47" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>65</v>
       </c>
@@ -3925,10 +3923,10 @@
       <c r="G47" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+    </row>
+    <row r="48" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>65</v>
       </c>
@@ -3950,10 +3948,10 @@
       <c r="G48" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+    </row>
+    <row r="49" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>65</v>
       </c>
@@ -3975,10 +3973,10 @@
       <c r="G49" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+    </row>
+    <row r="50" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>65</v>
       </c>
@@ -4000,10 +3998,10 @@
       <c r="G50" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+    </row>
+    <row r="51" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>65</v>
       </c>
@@ -4025,10 +4023,10 @@
       <c r="G51" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+    </row>
+    <row r="52" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>65</v>
       </c>
@@ -4050,10 +4048,10 @@
       <c r="G52" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+    </row>
+    <row r="53" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>65</v>
       </c>
@@ -4075,10 +4073,10 @@
       <c r="G53" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+    </row>
+    <row r="54" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>65</v>
       </c>
@@ -4100,10 +4098,10 @@
       <c r="G54" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+    </row>
+    <row r="55" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>65</v>
       </c>
@@ -4125,10 +4123,10 @@
       <c r="G55" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+    </row>
+    <row r="56" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>65</v>
       </c>
@@ -4150,10 +4148,10 @@
       <c r="G56" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+    </row>
+    <row r="57" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>65</v>
       </c>
@@ -4175,10 +4173,10 @@
       <c r="G57" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+    </row>
+    <row r="58" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>65</v>
       </c>
@@ -4200,10 +4198,10 @@
       <c r="G58" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+    </row>
+    <row r="59" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>65</v>
       </c>
@@ -4225,10 +4223,10 @@
       <c r="G59" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+    </row>
+    <row r="60" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>65</v>
       </c>
@@ -4250,10 +4248,10 @@
       <c r="G60" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+    </row>
+    <row r="61" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>65</v>
       </c>
@@ -4275,10 +4273,10 @@
       <c r="G61" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+    </row>
+    <row r="62" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>65</v>
       </c>
@@ -4300,10 +4298,10 @@
       <c r="G62" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+    </row>
+    <row r="63" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>65</v>
       </c>
@@ -4325,10 +4323,10 @@
       <c r="G63" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+    </row>
+    <row r="64" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>65</v>
       </c>
@@ -4350,10 +4348,10 @@
       <c r="G64" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+    </row>
+    <row r="65" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>65</v>
       </c>
@@ -4375,10 +4373,10 @@
       <c r="G65" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+    </row>
+    <row r="66" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>65</v>
       </c>
@@ -4400,10 +4398,10 @@
       <c r="G66" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+    </row>
+    <row r="67" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>65</v>
       </c>
@@ -4425,10 +4423,10 @@
       <c r="G67" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+    </row>
+    <row r="68" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>65</v>
       </c>
@@ -4450,10 +4448,10 @@
       <c r="G68" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+    </row>
+    <row r="69" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>65</v>
       </c>
@@ -4475,10 +4473,10 @@
       <c r="G69" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+    </row>
+    <row r="70" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>65</v>
       </c>
@@ -4500,10 +4498,10 @@
       <c r="G70" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+    </row>
+    <row r="71" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>65</v>
       </c>
@@ -4525,10 +4523,10 @@
       <c r="G71" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+    </row>
+    <row r="72" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>65</v>
       </c>
@@ -4550,10 +4548,10 @@
       <c r="G72" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+    </row>
+    <row r="73" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>65</v>
       </c>
@@ -4575,10 +4573,10 @@
       <c r="G73" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+    </row>
+    <row r="74" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>65</v>
       </c>
@@ -4600,10 +4598,10 @@
       <c r="G74" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I74" s="10"/>
-      <c r="J74" s="10"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+    </row>
+    <row r="75" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>65</v>
       </c>
@@ -4625,10 +4623,10 @@
       <c r="G75" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+    </row>
+    <row r="76" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>65</v>
       </c>
@@ -4650,10 +4648,10 @@
       <c r="G76" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I76" s="10"/>
-      <c r="J76" s="10"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
+    </row>
+    <row r="77" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>65</v>
       </c>
@@ -4675,10 +4673,10 @@
       <c r="G77" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+    </row>
+    <row r="78" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>65</v>
       </c>
@@ -4700,10 +4698,10 @@
       <c r="G78" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I78" s="10"/>
-      <c r="J78" s="10"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+    </row>
+    <row r="79" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>65</v>
       </c>
@@ -4725,10 +4723,10 @@
       <c r="G79" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+    </row>
+    <row r="80" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>65</v>
       </c>
@@ -4750,10 +4748,10 @@
       <c r="G80" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I80" s="10"/>
-      <c r="J80" s="10"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+    </row>
+    <row r="81" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>65</v>
       </c>
@@ -4775,10 +4773,10 @@
       <c r="G81" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+    </row>
+    <row r="82" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>65</v>
       </c>
@@ -4800,10 +4798,10 @@
       <c r="G82" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I82" s="10"/>
-      <c r="J82" s="10"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+    </row>
+    <row r="83" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>65</v>
       </c>
@@ -4825,10 +4823,10 @@
       <c r="G83" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I83" s="10"/>
-      <c r="J83" s="10"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
+    </row>
+    <row r="84" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>65</v>
       </c>
@@ -4850,10 +4848,10 @@
       <c r="G84" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I84" s="10"/>
-      <c r="J84" s="10"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
+    </row>
+    <row r="85" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>65</v>
       </c>
@@ -4875,10 +4873,10 @@
       <c r="G85" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+    </row>
+    <row r="86" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>65</v>
       </c>
@@ -4900,10 +4898,10 @@
       <c r="G86" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I86" s="10"/>
-      <c r="J86" s="10"/>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I86" s="6"/>
+      <c r="J86" s="6"/>
+    </row>
+    <row r="87" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>65</v>
       </c>
@@ -4925,10 +4923,10 @@
       <c r="G87" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I87" s="10"/>
-      <c r="J87" s="10"/>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
+    </row>
+    <row r="88" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>65</v>
       </c>
@@ -4950,10 +4948,10 @@
       <c r="G88" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="I88" s="10"/>
-      <c r="J88" s="10"/>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
+    </row>
+    <row r="89" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>65</v>
       </c>
@@ -4975,10 +4973,10 @@
       <c r="G89" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="I89" s="10"/>
-      <c r="J89" s="10"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
+    </row>
+    <row r="90" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>65</v>
       </c>
@@ -5000,10 +4998,10 @@
       <c r="G90" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I90" s="10"/>
-      <c r="J90" s="10"/>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+    </row>
+    <row r="91" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>65</v>
       </c>
@@ -5025,10 +5023,10 @@
       <c r="G91" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I91" s="10"/>
-      <c r="J91" s="10"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I91" s="6"/>
+      <c r="J91" s="6"/>
+    </row>
+    <row r="92" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>65</v>
       </c>
@@ -5050,10 +5048,10 @@
       <c r="G92" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="I92" s="10"/>
-      <c r="J92" s="10"/>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I92" s="6"/>
+      <c r="J92" s="6"/>
+    </row>
+    <row r="93" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>65</v>
       </c>
@@ -5075,10 +5073,10 @@
       <c r="G93" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I93" s="10"/>
-      <c r="J93" s="10"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I93" s="6"/>
+      <c r="J93" s="6"/>
+    </row>
+    <row r="94" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>65</v>
       </c>
@@ -5100,10 +5098,10 @@
       <c r="G94" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I94" s="10"/>
-      <c r="J94" s="10"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+    </row>
+    <row r="95" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>65</v>
       </c>
@@ -5125,10 +5123,10 @@
       <c r="G95" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I95" s="10"/>
-      <c r="J95" s="10"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I95" s="6"/>
+      <c r="J95" s="6"/>
+    </row>
+    <row r="96" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>65</v>
       </c>
@@ -5150,10 +5148,10 @@
       <c r="G96" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="I96" s="10"/>
-      <c r="J96" s="10"/>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I96" s="6"/>
+      <c r="J96" s="6"/>
+    </row>
+    <row r="97" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>65</v>
       </c>
@@ -5175,10 +5173,10 @@
       <c r="G97" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I97" s="10"/>
-      <c r="J97" s="10"/>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
+    </row>
+    <row r="98" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>65</v>
       </c>
@@ -5200,10 +5198,10 @@
       <c r="G98" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I98" s="10"/>
-      <c r="J98" s="10"/>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+    </row>
+    <row r="99" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>65</v>
       </c>
@@ -5225,10 +5223,10 @@
       <c r="G99" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="I99" s="10"/>
-      <c r="J99" s="10"/>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+    </row>
+    <row r="100" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>65</v>
       </c>
@@ -5250,10 +5248,10 @@
       <c r="G100" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="I100" s="10"/>
-      <c r="J100" s="10"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+    </row>
+    <row r="101" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>65</v>
       </c>
@@ -5275,8 +5273,8 @@
       <c r="G101" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I101" s="10"/>
-      <c r="J101" s="10"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -5288,15 +5286,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3747A4-993E-4CA6-B3B1-148509345593}">
   <dimension ref="A1:C35"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.875" style="9" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" style="9" customWidth="1"/>
     <col min="4" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>347</v>
       </c>
@@ -5307,369 +5305,369 @@
         <v>346</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="C11" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C14" s="11"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="C14" s="10"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="C26" s="11"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="11" t="s">
+      <c r="C26" s="10"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="11"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="11" t="s">
+      <c r="C27" s="10"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="10">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="C31" s="11"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+      <c r="C31" s="10"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="11" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="10" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="11" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="10" t="s">
         <v>205</v>
       </c>
     </row>

--- a/src/main/resources/excel_data/fact_data.xlsx
+++ b/src/main/resources/excel_data/fact_data.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P190184\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42B0221-997B-4493-A080-872BBBCF8AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9B05F8-8E94-4A50-BD5E-781157AF7633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cust_svc" sheetId="4" r:id="rId1"/>
     <sheet name="cust_prod" sheetId="2" r:id="rId2"/>
     <sheet name="eqp_mdl" sheetId="3" r:id="rId3"/>
     <sheet name="cons_itm_val" sheetId="5" r:id="rId4"/>
+    <sheet name="error_msg" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8779" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8912" uniqueCount="921">
   <si>
     <t>NA00000262</t>
   </si>
@@ -2517,6 +2518,343 @@
   </si>
   <si>
     <t>서비스변경사유코드</t>
+  </si>
+  <si>
+    <t>CONDCP000000003</t>
+  </si>
+  <si>
+    <t>MCP0000003</t>
+  </si>
+  <si>
+    <t>#01은 상품 가입해지 및 요금제변경 처리불가능합니다.</t>
+  </si>
+  <si>
+    <t>이용종류코드명</t>
+  </si>
+  <si>
+    <t>CONDCP000003252</t>
+  </si>
+  <si>
+    <t>MCP0003096</t>
+  </si>
+  <si>
+    <t>해당 단말에서 사용가능한 전용요금제가 아닙니다.</t>
+  </si>
+  <si>
+    <t>CONDCCP00000143</t>
+  </si>
+  <si>
+    <t>MCP0004002</t>
+  </si>
+  <si>
+    <t>eSIM단말 개통 진행중입니다. 개통완료 또는 취소후 업무처리 가능합니다.</t>
+  </si>
+  <si>
+    <t>CONDCP000003570</t>
+  </si>
+  <si>
+    <t>MCP0003570</t>
+  </si>
+  <si>
+    <t>외교/공부/협정, 미8군, 단기체류자는 처리불가능한 요금제입니다.</t>
+  </si>
+  <si>
+    <t>고객세부유형코드</t>
+  </si>
+  <si>
+    <t>CONDCP000003116</t>
+  </si>
+  <si>
+    <t>MCP0003116</t>
+  </si>
+  <si>
+    <t>아이키즈요금제만 가능한 단말기입니다</t>
+  </si>
+  <si>
+    <t>CONDCP000003083</t>
+  </si>
+  <si>
+    <t>MCP0003083</t>
+  </si>
+  <si>
+    <t>로밍 사용중 요금변경 불가한 요금제 입니다</t>
+  </si>
+  <si>
+    <t>CONDCP000003084</t>
+  </si>
+  <si>
+    <t>MCP0003084</t>
+  </si>
+  <si>
+    <t>로밍충전용품 사용중 요금변경 불가한 요금제 입니다</t>
+  </si>
+  <si>
+    <t>CONDCP000000051</t>
+  </si>
+  <si>
+    <t>MCP0000050</t>
+  </si>
+  <si>
+    <t>#01 이후에 T할부지원을 가입 하셨습니다</t>
+  </si>
+  <si>
+    <t>T할부지원 가입가능요금제로 변경하거나 T할부지원 취소 후 요금제 변경이 가능합니다</t>
+  </si>
+  <si>
+    <t>T할부지원가입시작일자</t>
+  </si>
+  <si>
+    <t>TCONDCCP0000341</t>
+  </si>
+  <si>
+    <t>MCP0042721</t>
+  </si>
+  <si>
+    <t>상품[#01] 가입가능한 연령대가 아닙니다(만 34이하만 가능)</t>
+  </si>
+  <si>
+    <t>상품명</t>
+  </si>
+  <si>
+    <t>CONDCP000000010</t>
+  </si>
+  <si>
+    <t>MCP0000010</t>
+  </si>
+  <si>
+    <t>당일 3회까지만 요금변경 가능합니다.</t>
+  </si>
+  <si>
+    <t>CONDCP000003027</t>
+  </si>
+  <si>
+    <t>MCP0003027</t>
+  </si>
+  <si>
+    <t>아이키즈요금제만 가능한 단말기입니다.</t>
+  </si>
+  <si>
+    <t>CONDCP000000070</t>
+  </si>
+  <si>
+    <t>MCP0000070</t>
+  </si>
+  <si>
+    <t>CONDCP000000071</t>
+  </si>
+  <si>
+    <t>MCP0000071</t>
+  </si>
+  <si>
+    <t>안심폰 요금제만 가능한 가능한 단말기입니다</t>
+  </si>
+  <si>
+    <t>CONDCP000000072</t>
+  </si>
+  <si>
+    <t>MCP0000072</t>
+  </si>
+  <si>
+    <t>TMS 복지 요금제만 가능한 단말기입니다</t>
+  </si>
+  <si>
+    <t>CONDCP000000073</t>
+  </si>
+  <si>
+    <t>MCP0000073</t>
+  </si>
+  <si>
+    <t>사회안전망요금제만 가능한 단말기입니다</t>
+  </si>
+  <si>
+    <t>TCONDCCP0000110</t>
+  </si>
+  <si>
+    <t>MCP0042697</t>
+  </si>
+  <si>
+    <t>요금제 가입불가(T다이렉트샵에서 개통 후 14일 이내만 가입할 수 있음)</t>
+  </si>
+  <si>
+    <t>TCONDCCP0000105</t>
+  </si>
+  <si>
+    <t>MCP0042722</t>
+  </si>
+  <si>
+    <t>다이렉트 요금제 가입시 승계불가 T지원금약정은 선해지 후 가능합니다.</t>
+  </si>
+  <si>
+    <t>CONDCP000003126</t>
+  </si>
+  <si>
+    <t>MCP0003126</t>
+  </si>
+  <si>
+    <t>어린이/청소년/청년 요금제 가입가능 회선수 초과입니다</t>
+  </si>
+  <si>
+    <t>TCONDCP00000008</t>
+  </si>
+  <si>
+    <t>MCP0042723</t>
+  </si>
+  <si>
+    <t>[#01] 가입 가능한 고객유형이 아닙니다.</t>
+  </si>
+  <si>
+    <t>CONDCP000000470</t>
+  </si>
+  <si>
+    <t>MCP0000400</t>
+  </si>
+  <si>
+    <t>#01 이용종류에 사용가능한 상품이 아닙니다</t>
+  </si>
+  <si>
+    <t>CONDCP000000482</t>
+  </si>
+  <si>
+    <t>MCP0000482</t>
+  </si>
+  <si>
+    <t>#01 가능부가상품 이용종류에 사용불가능한 상품[ #02] 입니다(PPS)</t>
+  </si>
+  <si>
+    <t>이용종류명/상품명</t>
+  </si>
+  <si>
+    <t>CONDCP000003646</t>
+  </si>
+  <si>
+    <t>MCP0003646</t>
+  </si>
+  <si>
+    <t>#01 가능부가상품 이용종류에 사용불가능한 상품[ #02] 입니다(HDN)</t>
+  </si>
+  <si>
+    <t>CONDCCP00000275</t>
+  </si>
+  <si>
+    <t>MCP0000500</t>
+  </si>
+  <si>
+    <t>현 단말기에 사용 할 수 없는 상품[#01] 입니다.</t>
+  </si>
+  <si>
+    <t>CONDCP000000440</t>
+  </si>
+  <si>
+    <t>CONDCP000042611</t>
+  </si>
+  <si>
+    <t>MCP0042541</t>
+  </si>
+  <si>
+    <t>T원넘버_공유II(모) 사용중에 변경 불가능한 요금제(#01) 입니다.</t>
+  </si>
+  <si>
+    <t>CONDCCP00000222</t>
+  </si>
+  <si>
+    <t>MCP0042614</t>
+  </si>
+  <si>
+    <t>원넘버 동시착신형 사용중에 변경 불가능한 요금제(#01) 입니다.</t>
+  </si>
+  <si>
+    <t>CONDCCP00000310</t>
+  </si>
+  <si>
+    <t>MCP0004005</t>
+  </si>
+  <si>
+    <t>상품 가입/해지 처리는 권한자만 가능합니다.</t>
+  </si>
+  <si>
+    <t>CONDCCP00000110</t>
+  </si>
+  <si>
+    <t>MCP0004000</t>
+  </si>
+  <si>
+    <t>해당 요금제는 부가상품 처리 불가합니다.</t>
+  </si>
+  <si>
+    <t>CONDCP000042639</t>
+  </si>
+  <si>
+    <t>MCP0042676</t>
+  </si>
+  <si>
+    <t>동일 단말기 다른 서비스에 #01 과 동일유형 상품을 사용중이므로 가입처리 불가능합니다.</t>
+  </si>
+  <si>
+    <t>CONDCP000042614</t>
+  </si>
+  <si>
+    <t>MCP0042543</t>
+  </si>
+  <si>
+    <t>Apple Watch에서 처리할수 없는 상품(#01) 입니다</t>
+  </si>
+  <si>
+    <t>CONDCP000000033</t>
+  </si>
+  <si>
+    <t>MCP0000032</t>
+  </si>
+  <si>
+    <t>상품[#01] 가입가능한 연령대가 아닙니다(만 65이상만 가능)</t>
+  </si>
+  <si>
+    <t>CONDCCP00000353</t>
+  </si>
+  <si>
+    <t>MCP0003125</t>
+  </si>
+  <si>
+    <t>#01는 고객기준 1회선만 사용 가능합니다.</t>
+  </si>
+  <si>
+    <t>CONDCP000000364</t>
+  </si>
+  <si>
+    <t>MCP0000363</t>
+  </si>
+  <si>
+    <t>처리 가능한 고객유형 #01 상품이 아닙니다</t>
+  </si>
+  <si>
+    <t>CONDCCP00000051</t>
+  </si>
+  <si>
+    <t>CONDCCP00000098</t>
+  </si>
+  <si>
+    <t>CONDCP000003335</t>
+  </si>
+  <si>
+    <t>MCP0000446</t>
+  </si>
+  <si>
+    <t>#01 이용종류에 사용가능한 요금제가 아닙니다</t>
+  </si>
+  <si>
+    <t>COND_CONS_ID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSG_ID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSG_CTT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MSG_INFO</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2628,7 +2966,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2666,6 +3004,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2679,7 +3043,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2705,6 +3069,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -32646,6 +33016,518 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADCF59F8-FA60-42B6-815E-044766B7E99E}">
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24" style="3" customWidth="1"/>
+    <col min="2" max="2" width="18" style="3" customWidth="1"/>
+    <col min="3" max="3" width="67.5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="33.25" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>810</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>811</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>812</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>814</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>815</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>816</v>
+      </c>
+      <c r="D3" s="12"/>
+    </row>
+    <row r="4" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>817</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="D4" s="12"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>820</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="D6" s="12"/>
+    </row>
+    <row r="7" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="D7" s="12"/>
+    </row>
+    <row r="8" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>832</v>
+      </c>
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>833</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>834</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>835</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14" t="s">
+        <v>836</v>
+      </c>
+      <c r="D10" s="14"/>
+    </row>
+    <row r="11" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>840</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>842</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>843</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>844</v>
+      </c>
+      <c r="D12" s="12"/>
+    </row>
+    <row r="13" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>845</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>847</v>
+      </c>
+      <c r="D13" s="12"/>
+    </row>
+    <row r="14" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>848</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>849</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="D14" s="12"/>
+    </row>
+    <row r="15" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>852</v>
+      </c>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>853</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>855</v>
+      </c>
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>856</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>857</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>858</v>
+      </c>
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>859</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>860</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>861</v>
+      </c>
+      <c r="D18" s="12"/>
+    </row>
+    <row r="19" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>864</v>
+      </c>
+      <c r="D19" s="12"/>
+    </row>
+    <row r="20" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>865</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>866</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="D20" s="12"/>
+    </row>
+    <row r="21" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>869</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>870</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>871</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>875</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>876</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>879</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>880</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>884</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>886</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>887</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>888</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>889</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>890</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>891</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>892</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>893</v>
+      </c>
+      <c r="D29" s="12"/>
+    </row>
+    <row r="30" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>894</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>895</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>896</v>
+      </c>
+      <c r="D30" s="12"/>
+    </row>
+    <row r="31" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>897</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>898</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
+        <v>900</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>901</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>902</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>903</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>904</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>905</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>906</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>908</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
+        <v>909</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>910</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>911</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>912</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
+        <v>913</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>883</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>914</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>915</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>916</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>813</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{14a54c8a-2b3f-4f0b-928a-376f2f2beb46}" enabled="1" method="Privileged" siteId="{5afa09fd-c4be-434d-830d-f4765c449035}" contentBits="0" removed="0"/>

--- a/src/main/resources/excel_data/fact_data.xlsx
+++ b/src/main/resources/excel_data/fact_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P190184\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DevSrc\260429\SKT-BAMOE-POC\src\main\resources\excel_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9B05F8-8E94-4A50-BD5E-781157AF7633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACD0F76-1F8F-4EB8-B786-CF9C87A2903B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cust_svc" sheetId="4" r:id="rId1"/>
@@ -33,12 +33,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8912" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8911" uniqueCount="920">
   <si>
     <t>NA00000262</t>
   </si>
@@ -2595,12 +2598,6 @@
     <t>MCP0000050</t>
   </si>
   <si>
-    <t>#01 이후에 T할부지원을 가입 하셨습니다</t>
-  </si>
-  <si>
-    <t>T할부지원 가입가능요금제로 변경하거나 T할부지원 취소 후 요금제 변경이 가능합니다</t>
-  </si>
-  <si>
     <t>T할부지원가입시작일자</t>
   </si>
   <si>
@@ -2854,6 +2851,10 @@
   </si>
   <si>
     <t>MSG_INFO</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>#01 이후에 T할부지원을 가입 하셨습니다. T할부지원 가입가능요금제로 변경하거나 T할부지원 취소 후 요금제 변경이 가능합니다</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2966,7 +2967,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3004,32 +3005,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3043,7 +3018,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3071,10 +3046,7 @@
     <xf numFmtId="49" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -33018,117 +32990,117 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADCF59F8-FA60-42B6-815E-044766B7E99E}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" style="3" customWidth="1"/>
-    <col min="2" max="2" width="18" style="3" customWidth="1"/>
-    <col min="3" max="3" width="67.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="33.25" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>916</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>917</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="11" t="s">
         <v>918</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>919</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>810</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>811</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>812</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>814</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>815</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>816</v>
       </c>
-      <c r="D3" s="12"/>
-    </row>
-    <row r="4" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="D3" s="13"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
         <v>817</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>818</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>819</v>
       </c>
-      <c r="D4" s="12"/>
-    </row>
-    <row r="5" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+      <c r="D4" s="13"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>820</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>821</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>822</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>824</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>825</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>826</v>
       </c>
-      <c r="D6" s="12"/>
-    </row>
-    <row r="7" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="D6" s="13"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>827</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>828</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>829</v>
       </c>
-      <c r="D7" s="12"/>
-    </row>
-    <row r="8" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
         <v>830</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>831</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>832</v>
       </c>
-      <c r="D8" s="12"/>
+      <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
@@ -33138,393 +33110,386 @@
         <v>834</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>919</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>835</v>
       </c>
-      <c r="D9" s="13" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>836</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14" t="s">
-        <v>836</v>
-      </c>
-      <c r="D10" s="14"/>
-    </row>
-    <row r="11" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>838</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>839</v>
       </c>
-      <c r="C11" s="12" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>840</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>841</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+      <c r="C11" s="13" t="s">
         <v>842</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="D11" s="13"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>843</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="13" t="s">
         <v>844</v>
       </c>
-      <c r="D12" s="12"/>
-    </row>
-    <row r="13" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>845</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="D12" s="13"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>846</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>847</v>
       </c>
-      <c r="D13" s="12"/>
-    </row>
-    <row r="14" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="C13" s="13" t="s">
+        <v>826</v>
+      </c>
+      <c r="D13" s="13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
         <v>848</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>849</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>826</v>
-      </c>
-      <c r="D14" s="12"/>
-    </row>
-    <row r="15" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>850</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="D14" s="13"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>851</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="B15" s="13" t="s">
         <v>852</v>
       </c>
-      <c r="D15" s="12"/>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>853</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
         <v>854</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="B16" s="13" t="s">
         <v>855</v>
       </c>
-      <c r="D16" s="12"/>
-    </row>
-    <row r="17" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>856</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="D16" s="13"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>857</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>858</v>
       </c>
-      <c r="D17" s="12"/>
-    </row>
-    <row r="18" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>859</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="D17" s="13"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
         <v>860</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="B18" s="13" t="s">
         <v>861</v>
       </c>
-      <c r="D18" s="12"/>
-    </row>
-    <row r="19" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="D18" s="13"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>863</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="B19" s="13" t="s">
         <v>864</v>
       </c>
-      <c r="D19" s="12"/>
-    </row>
-    <row r="20" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>865</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="D19" s="13"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="13" t="s">
         <v>866</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="B20" s="13" t="s">
         <v>867</v>
       </c>
-      <c r="D20" s="12"/>
-    </row>
-    <row r="21" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>868</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="D20" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>869</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="B21" s="13" t="s">
         <v>870</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+      <c r="C21" s="13" t="s">
         <v>871</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="D21" s="13" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="13" t="s">
         <v>872</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="B22" s="13" t="s">
         <v>873</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="C22" s="13" t="s">
+        <v>874</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>876</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>877</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>878</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>879</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>880</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>881</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>882</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>870</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>871</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>874</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>875</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>876</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
-        <v>878</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>879</v>
-      </c>
-      <c r="C24" s="12" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="13" t="s">
+        <v>883</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>884</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>885</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
+        <v>886</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>888</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="13" t="s">
+        <v>889</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>890</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>891</v>
+      </c>
+      <c r="D28" s="13"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
+        <v>892</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>893</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>894</v>
+      </c>
+      <c r="D29" s="13"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="13" t="s">
+        <v>895</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>896</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>897</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
+        <v>898</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>899</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>900</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="13" t="s">
+        <v>901</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>902</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>903</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
+        <v>904</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>905</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>906</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="13" t="s">
+        <v>907</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>908</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>909</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
+        <v>910</v>
+      </c>
+      <c r="B35" s="13" t="s">
         <v>880</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>881</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>882</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>883</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
-        <v>884</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>872</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>873</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
-        <v>885</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>886</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>887</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
-        <v>888</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>889</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>890</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
-        <v>891</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>892</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>893</v>
-      </c>
-      <c r="D29" s="12"/>
-    </row>
-    <row r="30" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
-        <v>894</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>895</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>896</v>
-      </c>
-      <c r="D30" s="12"/>
-    </row>
-    <row r="31" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
-        <v>897</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>898</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>899</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="12" t="s">
-        <v>900</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>901</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>902</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="12" t="s">
-        <v>903</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>904</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>905</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="12" t="s">
-        <v>906</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>907</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>908</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
-        <v>909</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>910</v>
-      </c>
-      <c r="C35" s="12" t="s">
+      <c r="D35" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="13" t="s">
         <v>911</v>
       </c>
-      <c r="D35" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="12" t="s">
+      <c r="B36" s="13" t="s">
+        <v>880</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>881</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>912</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>882</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>883</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="12" t="s">
+      <c r="B37" s="13" t="s">
         <v>913</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>882</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>883</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="14.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>915</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>916</v>
-      </c>
-      <c r="D38" s="12" t="s">
+      <c r="D37" s="13" t="s">
         <v>813</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
